--- a/AAII_Financials/Yearly/DUK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DUK_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
   <si>
     <t>DUK</t>
   </si>
@@ -656,196 +656,208 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:P102"/>
+  <dimension ref="A5:Q102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="14" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>44926</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44561</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44196</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>43830</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43465</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43100</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>42735</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42369</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42004</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>41639</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41274</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>40908</v>
       </c>
-      <c r="P7" s="2"/>
-    </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>29060000</v>
+      </c>
+      <c r="E8" s="3">
         <v>28768000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>24621000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>23366000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>25079000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>24521000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>23565000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>22743000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>22371000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>22509000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>22756000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>17912000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>14529000</v>
       </c>
-      <c r="P8" s="3"/>
-    </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q8" s="3"/>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>15288000</v>
+      </c>
+      <c r="E9" s="3">
         <v>15792000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>12663000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>17625000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>13519000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13991000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>12926000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13114000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13389000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13956000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13545000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>16817000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>8915000</v>
       </c>
-      <c r="P9" s="3"/>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q9" s="3"/>
+    </row>
+    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>13772000</v>
+      </c>
+      <c r="E10" s="3">
         <v>12976000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>11958000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>5741000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>11560000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>10530000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>10639000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>9629000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>8982000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8553000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>9211000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>1095000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>5614000</v>
       </c>
-      <c r="P10" s="3"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q10" s="3"/>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -862,8 +874,9 @@
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q11" s="3"/>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -903,9 +916,12 @@
       <c r="O12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P12" s="3"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q12" s="3"/>
+    </row>
+    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -945,93 +961,102 @@
       <c r="O13" s="3">
         <v>0</v>
       </c>
-      <c r="P13" s="3"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="P13" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="3"/>
+    </row>
+    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>49000</v>
+      </c>
+      <c r="E14" s="3">
         <v>412000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>341000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>1143000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>-4000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>491000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>254000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>-9000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>106000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>81000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>399000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>666000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>335000</v>
       </c>
-      <c r="P14" s="3"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q14" s="3"/>
+    </row>
+    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5253000</v>
+      </c>
+      <c r="E15" s="3">
         <v>5086000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>4762000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>9209000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4548000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4074000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>3527000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3294000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3053000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>2969000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2668000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2145000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>1806000</v>
       </c>
-      <c r="P15" s="3"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.2">
+      <c r="Q15" s="3"/>
+    </row>
+    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1045,92 +1070,99 @@
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
-    </row>
-    <row r="17" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q16" s="3"/>
+    </row>
+    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>21990000</v>
+      </c>
+      <c r="E17" s="3">
         <v>22756000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>19121000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>18795000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>19370000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>19836000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>17940000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17541000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17323000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17677000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17886000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>15011000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>11760000</v>
       </c>
-      <c r="P17" s="3"/>
-    </row>
-    <row r="18" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q17" s="3"/>
+    </row>
+    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>7070000</v>
+      </c>
+      <c r="E18" s="3">
         <v>6012000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>5500000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>4571000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5709000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>4685000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5625000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5202000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5048000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>4832000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4870000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>2901000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2769000</v>
       </c>
-      <c r="P18" s="3"/>
-    </row>
-    <row r="19" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q18" s="3"/>
+    </row>
+    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1147,218 +1179,234 @@
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
-    </row>
-    <row r="20" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q19" s="3"/>
+    </row>
+    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>711000</v>
+      </c>
+      <c r="E20" s="3">
         <v>505000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>698000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>608000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>592000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>482000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>627000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>448000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>389000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>460000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>254000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>577000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>555000</v>
       </c>
-      <c r="P20" s="3"/>
-    </row>
-    <row r="21" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q20" s="3"/>
+    </row>
+    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>13865000</v>
+      </c>
+      <c r="E21" s="3">
         <v>12360000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>11861000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>10665000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>11477000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>9863000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>10298000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9530000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9050000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>8799000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8353000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>6130000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>5350000</v>
       </c>
-      <c r="P21" s="3"/>
-    </row>
-    <row r="22" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q21" s="3"/>
+    </row>
+    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3014000</v>
+      </c>
+      <c r="E22" s="3">
         <v>2439000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2207000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>4259000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2204000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2094000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1986000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1916000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1527000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1529000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1329000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1244000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>859000</v>
       </c>
-      <c r="P22" s="3"/>
-    </row>
-    <row r="23" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q22" s="3"/>
+    </row>
+    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>4767000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4078000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>3991000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>920000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>4097000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>3073000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4266000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3734000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3910000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3763000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3795000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>2234000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2465000</v>
       </c>
-      <c r="P23" s="3"/>
-    </row>
-    <row r="24" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q23" s="3"/>
+    </row>
+    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>438000</v>
+      </c>
+      <c r="E24" s="3">
         <v>300000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>268000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>-169000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>519000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>428000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>1308000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1156000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1256000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1225000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1205000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>623000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>752000</v>
       </c>
-      <c r="P24" s="3"/>
-    </row>
-    <row r="25" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q24" s="3"/>
+    </row>
+    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1398,93 +1446,102 @@
       <c r="O25" s="3">
         <v>0</v>
       </c>
-      <c r="P25" s="3"/>
-    </row>
-    <row r="26" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P25" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="3"/>
+    </row>
+    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4329000</v>
+      </c>
+      <c r="E26" s="3">
         <v>3778000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3723000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>1089000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3578000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>2645000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2958000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2578000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2654000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2538000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2590000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>1611000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1713000</v>
       </c>
-      <c r="P26" s="3"/>
-    </row>
-    <row r="27" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q26" s="3"/>
+    </row>
+    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>4190000</v>
+      </c>
+      <c r="E27" s="3">
         <v>3767000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>3946000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>1277000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3714000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>2667000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2953000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2560000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2639000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2532000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2579000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>1597000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1705000</v>
       </c>
-      <c r="P27" s="3"/>
-    </row>
-    <row r="28" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q27" s="3"/>
+    </row>
+    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1524,51 +1581,57 @@
       <c r="O28" s="3">
         <v>0</v>
       </c>
-      <c r="P28" s="3"/>
-    </row>
-    <row r="29" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P28" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="3"/>
+    </row>
+    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>-1455000</v>
+      </c>
+      <c r="E29" s="3">
         <v>-1323000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-144000</v>
-      </c>
-      <c r="F29" s="3">
-        <v>-7000</v>
       </c>
       <c r="G29" s="3">
         <v>-7000</v>
       </c>
       <c r="H29" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="I29" s="3">
         <v>-1000</v>
       </c>
-      <c r="I29" s="3">
+      <c r="J29" s="3">
         <v>106000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-408000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>177000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-649000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>86000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>207000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>1000</v>
       </c>
-      <c r="P29" s="3"/>
-    </row>
-    <row r="30" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q29" s="3"/>
+    </row>
+    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1608,9 +1671,12 @@
       <c r="O30" s="3">
         <v>0</v>
       </c>
-      <c r="P30" s="3"/>
-    </row>
-    <row r="31" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3"/>
+    </row>
+    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1650,93 +1716,102 @@
       <c r="O31" s="3">
         <v>0</v>
       </c>
-      <c r="P31" s="3"/>
-    </row>
-    <row r="32" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P31" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="3"/>
+    </row>
+    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-711000</v>
+      </c>
+      <c r="E32" s="3">
         <v>-505000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-698000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-608000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-592000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-482000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-627000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-448000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-389000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-460000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-254000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-577000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-555000</v>
       </c>
-      <c r="P32" s="3"/>
-    </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q32" s="3"/>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>2735000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2444000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>3802000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>1270000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3707000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>2666000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3059000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2152000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2816000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>1883000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2665000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1804000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1706000</v>
       </c>
-      <c r="P33" s="3"/>
-    </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q33" s="3"/>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1776,98 +1851,107 @@
       <c r="O34" s="3">
         <v>0</v>
       </c>
-      <c r="P34" s="3"/>
-    </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P34" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="3"/>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>2735000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2444000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>3802000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>1270000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3707000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>2666000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3059000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2152000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2816000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>1883000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2665000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1804000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1706000</v>
       </c>
-      <c r="P35" s="3"/>
-    </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q35" s="3"/>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>44926</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44561</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44196</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>43830</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43465</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43100</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>42735</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42369</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42004</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>41639</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41274</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>40908</v>
       </c>
-      <c r="P38" s="2"/>
-    </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q38" s="2"/>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1884,8 +1968,9 @@
       <c r="N39" s="3"/>
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
-    </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q39" s="3"/>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1902,50 +1987,54 @@
       <c r="N40" s="3"/>
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
-    </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q40" s="3"/>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>253000</v>
+      </c>
+      <c r="E41" s="3">
         <v>409000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>343000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>259000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>311000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>442000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>358000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>392000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>383000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>2036000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1501000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1424000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>2110000</v>
       </c>
-      <c r="P41" s="3"/>
-    </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q41" s="3"/>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -1958,296 +2047,317 @@
       <c r="F42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G42" s="3">
+      <c r="G42" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H42" s="3">
         <v>18000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>37000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>35000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>111000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>18000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>178000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>333000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>190000</v>
       </c>
-      <c r="P42" s="3"/>
-    </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q42" s="3"/>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4131000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4415000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>3610000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3153000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3060000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3134000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2774000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2644000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2263000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2764000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>3005000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2717000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1941000</v>
       </c>
-      <c r="P43" s="3"/>
-    </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q43" s="3"/>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4292000</v>
+      </c>
+      <c r="E44" s="3">
         <v>3584000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3199000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3167000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3232000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3084000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3250000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3522000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3746000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3459000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>6500000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3223000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1588000</v>
       </c>
-      <c r="P44" s="3"/>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q44" s="3"/>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>4093000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4814000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>2788000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2103000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2542000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3017000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2036000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1370000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1924000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3662000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2734000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2425000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>1051000</v>
       </c>
-      <c r="P45" s="3"/>
-    </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q45" s="3"/>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12769000</v>
+      </c>
+      <c r="E46" s="3">
         <v>13222000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>9940000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>8682000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9163000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9714000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>8453000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8039000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8322000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>11575000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>10516000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10122000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6880000</v>
       </c>
-      <c r="P46" s="3"/>
-    </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q46" s="3"/>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>492000</v>
+      </c>
+      <c r="E47" s="3">
         <v>455000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>970000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>961000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1937000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1413000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1191000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>976000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>506000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3038000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>555000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>554000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>522000</v>
       </c>
-      <c r="P47" s="3"/>
-    </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q47" s="3"/>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>116407000</v>
+      </c>
+      <c r="E48" s="3">
         <v>225571000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>112674000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>108306000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>103785000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>91694000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>86391000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>82520000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>73779000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>70046000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>170639000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>68558000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>42661000</v>
       </c>
-      <c r="P48" s="3"/>
-    </row>
-    <row r="49" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q48" s="3"/>
+    </row>
+    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>19303000</v>
+      </c>
+      <c r="E49" s="3">
         <v>38606000</v>
-      </c>
-      <c r="E49" s="3">
-        <v>19303000</v>
       </c>
       <c r="F49" s="3">
         <v>19303000</v>
@@ -2259,29 +2369,32 @@
         <v>19303000</v>
       </c>
       <c r="I49" s="3">
+        <v>19303000</v>
+      </c>
+      <c r="J49" s="3">
         <v>19396000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>19425000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>16072000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>16321000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>32680000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>16737000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>4212000</v>
       </c>
-      <c r="P49" s="3"/>
-    </row>
-    <row r="50" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q49" s="3"/>
+    </row>
+    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2321,9 +2434,12 @@
       <c r="O50" s="3">
         <v>0</v>
       </c>
-      <c r="P50" s="3"/>
-    </row>
-    <row r="51" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P50" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q50" s="3"/>
+    </row>
+    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2363,51 +2479,57 @@
       <c r="O51" s="3">
         <v>0</v>
       </c>
-      <c r="P51" s="3"/>
-    </row>
-    <row r="52" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P51" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q51" s="3"/>
+    </row>
+    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>27922000</v>
+      </c>
+      <c r="E52" s="3">
         <v>32316000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>26700000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>25136000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>24650000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>23268000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>22483000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>21801000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>25562000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>25398000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>17878000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>17885000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8251000</v>
       </c>
-      <c r="P52" s="3"/>
-    </row>
-    <row r="53" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q52" s="3"/>
+    </row>
+    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2447,51 +2569,57 @@
       <c r="O53" s="3">
         <v>0</v>
       </c>
-      <c r="P53" s="3"/>
-    </row>
-    <row r="54" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P53" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="3"/>
+    </row>
+    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>176893000</v>
+      </c>
+      <c r="E54" s="3">
         <v>178086000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>169587000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>162388000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>158838000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>145392000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>137914000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>132761000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>121156000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>120557000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>114779000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>113856000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>62526000</v>
       </c>
-      <c r="P54" s="3"/>
-    </row>
-    <row r="55" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q54" s="3"/>
+    </row>
+    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2508,8 +2636,9 @@
       <c r="N55" s="3"/>
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
-    </row>
-    <row r="56" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q55" s="3"/>
+    </row>
+    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2526,260 +2655,279 @@
       <c r="N56" s="3"/>
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
-    </row>
-    <row r="57" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q56" s="3"/>
+    </row>
+    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>4228000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4754000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>3629000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3144000</v>
-      </c>
-      <c r="G57" s="3">
-        <v>3487000</v>
       </c>
       <c r="H57" s="3">
         <v>3487000</v>
       </c>
       <c r="I57" s="3">
+        <v>3487000</v>
+      </c>
+      <c r="J57" s="3">
         <v>3043000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>2994000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2350000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2271000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2391000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2444000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1433000</v>
       </c>
-      <c r="P57" s="3"/>
-    </row>
-    <row r="58" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q57" s="3"/>
+    </row>
+    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>7088000</v>
+      </c>
+      <c r="E58" s="3">
         <v>11984000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>6691000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>7111000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6276000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6816000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>5407000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4806000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5659000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5321000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>2943000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>4167000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2321000</v>
       </c>
-      <c r="P58" s="3"/>
-    </row>
-    <row r="59" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q58" s="3"/>
+    </row>
+    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5967000</v>
+      </c>
+      <c r="E59" s="3">
         <v>8456000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5611000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>6050000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4989000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>4738000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>4032000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3751000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>5506000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>6091000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>3617000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3418000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1774000</v>
       </c>
-      <c r="P59" s="3"/>
-    </row>
-    <row r="60" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q59" s="3"/>
+    </row>
+    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>17283000</v>
+      </c>
+      <c r="E60" s="3">
         <v>18873000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>15931000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>16305000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>14752000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>15041000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>12482000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>11551000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11400000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11233000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>8644000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>10029000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>5528000</v>
       </c>
-      <c r="P60" s="3"/>
-    </row>
-    <row r="61" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q60" s="3"/>
+    </row>
+    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>72452000</v>
+      </c>
+      <c r="E61" s="3">
         <v>65873000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>60448000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>55625000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>54985000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>51123000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>49035000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>45576000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>36842000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>37061000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>38152000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>36351000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>18679000</v>
       </c>
-      <c r="P61" s="3"/>
-    </row>
-    <row r="62" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q61" s="3"/>
+    </row>
+    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>36814000</v>
+      </c>
+      <c r="E62" s="3">
         <v>39560000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>42072000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>41274000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>41150000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>35394000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>34660000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>34593000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>33949000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>33004000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>26664000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>26535000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>15454000</v>
       </c>
-      <c r="P62" s="3"/>
-    </row>
-    <row r="63" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q62" s="3"/>
+    </row>
+    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2819,9 +2967,12 @@
       <c r="O63" s="3">
         <v>0</v>
       </c>
-      <c r="P63" s="3"/>
-    </row>
-    <row r="64" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P63" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q63" s="3"/>
+    </row>
+    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -2861,9 +3012,12 @@
       <c r="O64" s="3">
         <v>0</v>
       </c>
-      <c r="P64" s="3"/>
-    </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P64" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q64" s="3"/>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -2903,51 +3057,57 @@
       <c r="O65" s="3">
         <v>0</v>
       </c>
-      <c r="P65" s="3"/>
-    </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P65" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q65" s="3"/>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>127781000</v>
+      </c>
+      <c r="E66" s="3">
         <v>128764000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>120291000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>114424000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>112016000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>101575000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>96175000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>91728000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>81429000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>79682000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>73449000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>72993000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>39754000</v>
       </c>
-      <c r="P66" s="3"/>
-    </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q66" s="3"/>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -2964,8 +3124,9 @@
       <c r="N67" s="3"/>
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
-    </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q67" s="3"/>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3005,9 +3166,12 @@
       <c r="O68" s="3">
         <v>0</v>
       </c>
-      <c r="P68" s="3"/>
-    </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P68" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q68" s="3"/>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3047,9 +3211,12 @@
       <c r="O69" s="3">
         <v>0</v>
       </c>
-      <c r="P69" s="3"/>
-    </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P69" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q69" s="3"/>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3066,7 +3233,7 @@
         <v>1962000</v>
       </c>
       <c r="H70" s="3">
-        <v>0</v>
+        <v>1962000</v>
       </c>
       <c r="I70" s="3">
         <v>0</v>
@@ -3089,9 +3256,12 @@
       <c r="O70" s="3">
         <v>0</v>
       </c>
-      <c r="P70" s="3"/>
-    </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P70" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q70" s="3"/>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3131,51 +3301,57 @@
       <c r="O71" s="3">
         <v>0</v>
       </c>
-      <c r="P71" s="3"/>
-    </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P71" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q71" s="3"/>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2235000</v>
+      </c>
+      <c r="E72" s="3">
         <v>2637000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>3265000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2471000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>4108000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>3113000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3013000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2384000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2564000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2012000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2363000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1889000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1873000</v>
       </c>
-      <c r="P72" s="3"/>
-    </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q72" s="3"/>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3215,9 +3391,12 @@
       <c r="O73" s="3">
         <v>0</v>
       </c>
-      <c r="P73" s="3"/>
-    </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P73" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="3"/>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3257,9 +3436,12 @@
       <c r="O74" s="3">
         <v>0</v>
       </c>
-      <c r="P74" s="3"/>
-    </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P74" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q74" s="3"/>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3299,51 +3481,57 @@
       <c r="O75" s="3">
         <v>0</v>
       </c>
-      <c r="P75" s="3"/>
-    </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P75" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q75" s="3"/>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>47150000</v>
+      </c>
+      <c r="E76" s="3">
         <v>47360000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>47334000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>46002000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>44860000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>43817000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>41739000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>41033000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>39727000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>40875000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>41330000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>40863000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>22772000</v>
       </c>
-      <c r="P76" s="3"/>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="Q76" s="3"/>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3383,98 +3571,107 @@
       <c r="O77" s="3">
         <v>0</v>
       </c>
-      <c r="P77" s="3"/>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.2">
+      <c r="P77" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="3"/>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>44926</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44561</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44196</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>43830</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43465</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43100</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>42735</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42369</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42004</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>41639</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41274</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>40908</v>
       </c>
-      <c r="P80" s="2"/>
-    </row>
-    <row r="81" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q80" s="2"/>
+    </row>
+    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>2735000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2444000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>3802000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>1270000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3707000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>2666000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3059000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2152000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2816000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>1883000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2665000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1804000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1706000</v>
       </c>
-      <c r="P81" s="3"/>
-    </row>
-    <row r="82" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q81" s="3"/>
+    </row>
+    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3491,50 +3688,54 @@
       <c r="N82" s="3"/>
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
-    </row>
-    <row r="83" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q82" s="3"/>
+    </row>
+    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>6084000</v>
+      </c>
+      <c r="E83" s="3">
         <v>5843000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>5663000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>5486000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5176000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>4696000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4046000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>3880000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3613000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3507000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3229000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>2652000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2026000</v>
       </c>
-      <c r="P83" s="3"/>
-    </row>
-    <row r="84" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q83" s="3"/>
+    </row>
+    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3574,9 +3775,12 @@
       <c r="O84" s="3">
         <v>0</v>
       </c>
-      <c r="P84" s="3"/>
-    </row>
-    <row r="85" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P84" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="3"/>
+    </row>
+    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3616,9 +3820,12 @@
       <c r="O85" s="3">
         <v>0</v>
       </c>
-      <c r="P85" s="3"/>
-    </row>
-    <row r="86" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P85" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="3"/>
+    </row>
+    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3658,9 +3865,12 @@
       <c r="O86" s="3">
         <v>0</v>
       </c>
-      <c r="P86" s="3"/>
-    </row>
-    <row r="87" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P86" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="3"/>
+    </row>
+    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3700,9 +3910,12 @@
       <c r="O87" s="3">
         <v>0</v>
       </c>
-      <c r="P87" s="3"/>
-    </row>
-    <row r="88" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P87" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="3"/>
+    </row>
+    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3742,51 +3955,57 @@
       <c r="O88" s="3">
         <v>0</v>
       </c>
-      <c r="P88" s="3"/>
-    </row>
-    <row r="89" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P88" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="3"/>
+    </row>
+    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>9878000</v>
+      </c>
+      <c r="E89" s="3">
         <v>5927000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>8290000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8856000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8209000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>7186000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>6624000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7337000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7775000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>6038000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6382000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>5244000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>3672000</v>
       </c>
-      <c r="P89" s="3"/>
-    </row>
-    <row r="90" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q89" s="3"/>
+    </row>
+    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -3803,50 +4022,54 @@
       <c r="N90" s="3"/>
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
-    </row>
-    <row r="91" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q90" s="3"/>
+    </row>
+    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12604000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11367000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9715000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9907000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11122000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9389000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-8052000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7901000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-6766000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-5384000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5526000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5501000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4363000</v>
       </c>
-      <c r="P91" s="3"/>
-    </row>
-    <row r="92" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q91" s="3"/>
+    </row>
+    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -3886,9 +4109,12 @@
       <c r="O92" s="3">
         <v>0</v>
       </c>
-      <c r="P92" s="3"/>
-    </row>
-    <row r="93" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P92" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="3"/>
+    </row>
+    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -3928,51 +4154,57 @@
       <c r="O93" s="3">
         <v>0</v>
       </c>
-      <c r="P93" s="3"/>
-    </row>
-    <row r="94" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P93" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="3"/>
+    </row>
+    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-12475000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-11973000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10935000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10604000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11957000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10060000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8442000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11528000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-5277000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5373000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-4978000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-6197000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4434000</v>
       </c>
-      <c r="P94" s="3"/>
-    </row>
-    <row r="95" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q94" s="3"/>
+    </row>
+    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -3989,50 +4221,54 @@
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
-    </row>
-    <row r="96" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q95" s="3"/>
+    </row>
+    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>-3244000</v>
+      </c>
+      <c r="E96" s="3">
         <v>-3179000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>-3114000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>-2812000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>-2668000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>-2471000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>-2450000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>-2332000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2254000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2234000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2188000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-1752000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1329000</v>
       </c>
-      <c r="P96" s="3"/>
-    </row>
-    <row r="97" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q96" s="3"/>
+    </row>
+    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4072,9 +4308,12 @@
       <c r="O97" s="3">
         <v>0</v>
       </c>
-      <c r="P97" s="3"/>
-    </row>
-    <row r="98" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P97" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q97" s="3"/>
+    </row>
+    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4114,9 +4353,12 @@
       <c r="O98" s="3">
         <v>0</v>
       </c>
-      <c r="P98" s="3"/>
-    </row>
-    <row r="99" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P98" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q98" s="3"/>
+    </row>
+    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4156,51 +4398,57 @@
       <c r="O99" s="3">
         <v>0</v>
       </c>
-      <c r="P99" s="3"/>
-    </row>
-    <row r="100" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P99" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q99" s="3"/>
+    </row>
+    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>2351000</v>
+      </c>
+      <c r="E100" s="3">
         <v>6129000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2609000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>1731000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>3730000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>2960000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>1782000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>4251000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-2578000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-678000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-1327000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>267000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1202000</v>
       </c>
-      <c r="P100" s="3"/>
-    </row>
-    <row r="101" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="Q100" s="3"/>
+    </row>
+    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4240,49 +4488,55 @@
       <c r="O101" s="3">
         <v>0</v>
       </c>
-      <c r="P101" s="3"/>
-    </row>
-    <row r="102" spans="3:16" x14ac:dyDescent="0.2">
+      <c r="P101" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q101" s="3"/>
+    </row>
+    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-246000</v>
+      </c>
+      <c r="E102" s="3">
         <v>83000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-36000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-17000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-18000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>86000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-36000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>60000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-80000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-13000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>77000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-686000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>440000</v>
       </c>
-      <c r="P102" s="3"/>
+      <c r="Q102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/DUK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DUK_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
   <si>
     <t>DUK</t>
   </si>
@@ -727,25 +727,25 @@
         <v>3</v>
       </c>
       <c r="D8" s="3">
-        <v>29060000</v>
+        <v>28602000</v>
       </c>
       <c r="E8" s="3">
-        <v>28768000</v>
+        <v>28319000</v>
       </c>
       <c r="F8" s="3">
-        <v>24621000</v>
+        <v>24201000</v>
       </c>
       <c r="G8" s="3">
-        <v>23366000</v>
+        <v>22951000</v>
       </c>
       <c r="H8" s="3">
-        <v>25079000</v>
+        <v>24658000</v>
       </c>
       <c r="I8" s="3">
-        <v>24521000</v>
+        <v>24116000</v>
       </c>
       <c r="J8" s="3">
-        <v>23565000</v>
+        <v>23189000</v>
       </c>
       <c r="K8" s="3">
         <v>22743000</v>
@@ -772,25 +772,25 @@
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>15288000</v>
+        <v>14744000</v>
       </c>
       <c r="E9" s="3">
-        <v>15792000</v>
+        <v>15207000</v>
       </c>
       <c r="F9" s="3">
-        <v>12663000</v>
+        <v>12132000</v>
       </c>
       <c r="G9" s="3">
-        <v>17625000</v>
+        <v>11683000</v>
       </c>
       <c r="H9" s="3">
-        <v>13519000</v>
+        <v>13082000</v>
       </c>
       <c r="I9" s="3">
-        <v>13991000</v>
+        <v>13399000</v>
       </c>
       <c r="J9" s="3">
-        <v>12926000</v>
+        <v>12486000</v>
       </c>
       <c r="K9" s="3">
         <v>13114000</v>
@@ -817,25 +817,25 @@
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>13772000</v>
+        <v>13858000</v>
       </c>
       <c r="E10" s="3">
-        <v>12976000</v>
+        <v>13112000</v>
       </c>
       <c r="F10" s="3">
-        <v>11958000</v>
+        <v>12069000</v>
       </c>
       <c r="G10" s="3">
-        <v>5741000</v>
+        <v>11268000</v>
       </c>
       <c r="H10" s="3">
-        <v>11560000</v>
+        <v>11576000</v>
       </c>
       <c r="I10" s="3">
-        <v>10530000</v>
+        <v>10717000</v>
       </c>
       <c r="J10" s="3">
-        <v>10639000</v>
+        <v>10703000</v>
       </c>
       <c r="K10" s="3">
         <v>9629000</v>
@@ -971,25 +971,25 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>49000</v>
+        <v>135000</v>
       </c>
       <c r="E14" s="3">
-        <v>412000</v>
+        <v>548000</v>
       </c>
       <c r="F14" s="3">
-        <v>341000</v>
+        <v>469000</v>
       </c>
       <c r="G14" s="3">
-        <v>1143000</v>
+        <v>882000</v>
       </c>
       <c r="H14" s="3">
-        <v>-4000</v>
+        <v>12000</v>
       </c>
       <c r="I14" s="3">
-        <v>491000</v>
+        <v>677000</v>
       </c>
       <c r="J14" s="3">
-        <v>254000</v>
+        <v>313000</v>
       </c>
       <c r="K14" s="3">
         <v>-9000</v>
@@ -1022,10 +1022,10 @@
         <v>5086000</v>
       </c>
       <c r="F15" s="3">
-        <v>4762000</v>
+        <v>4745000</v>
       </c>
       <c r="G15" s="3">
-        <v>9209000</v>
+        <v>4504000</v>
       </c>
       <c r="H15" s="3">
         <v>4548000</v>
@@ -1077,25 +1077,25 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>21990000</v>
+        <v>21397000</v>
       </c>
       <c r="E17" s="3">
-        <v>22756000</v>
+        <v>21759000</v>
       </c>
       <c r="F17" s="3">
-        <v>19121000</v>
+        <v>18232000</v>
       </c>
       <c r="G17" s="3">
-        <v>18795000</v>
+        <v>17498000</v>
       </c>
       <c r="H17" s="3">
-        <v>19370000</v>
+        <v>18937000</v>
       </c>
       <c r="I17" s="3">
-        <v>19836000</v>
+        <v>18754000</v>
       </c>
       <c r="J17" s="3">
-        <v>17940000</v>
+        <v>17251000</v>
       </c>
       <c r="K17" s="3">
         <v>17541000</v>
@@ -1122,25 +1122,25 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>7070000</v>
+        <v>7205000</v>
       </c>
       <c r="E18" s="3">
-        <v>6012000</v>
+        <v>6560000</v>
       </c>
       <c r="F18" s="3">
-        <v>5500000</v>
+        <v>5969000</v>
       </c>
       <c r="G18" s="3">
-        <v>4571000</v>
+        <v>5453000</v>
       </c>
       <c r="H18" s="3">
-        <v>5709000</v>
+        <v>5721000</v>
       </c>
       <c r="I18" s="3">
-        <v>4685000</v>
+        <v>5362000</v>
       </c>
       <c r="J18" s="3">
-        <v>5625000</v>
+        <v>5938000</v>
       </c>
       <c r="K18" s="3">
         <v>5202000</v>
@@ -1186,25 +1186,25 @@
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>711000</v>
+        <v>-682000</v>
       </c>
       <c r="E20" s="3">
-        <v>505000</v>
+        <v>-478000</v>
       </c>
       <c r="F20" s="3">
-        <v>698000</v>
+        <v>-685000</v>
       </c>
       <c r="G20" s="3">
-        <v>608000</v>
+        <v>1584000</v>
       </c>
       <c r="H20" s="3">
-        <v>592000</v>
+        <v>-561000</v>
       </c>
       <c r="I20" s="3">
-        <v>482000</v>
+        <v>-462000</v>
       </c>
       <c r="J20" s="3">
-        <v>627000</v>
+        <v>-614000</v>
       </c>
       <c r="K20" s="3">
         <v>448000</v>
@@ -1231,25 +1231,25 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>13865000</v>
+        <v>13140000</v>
       </c>
       <c r="E21" s="3">
-        <v>12360000</v>
+        <v>12124000</v>
       </c>
       <c r="F21" s="3">
-        <v>11861000</v>
+        <v>11399000</v>
       </c>
       <c r="G21" s="3">
-        <v>10665000</v>
+        <v>8373000</v>
       </c>
       <c r="H21" s="3">
-        <v>11477000</v>
+        <v>10830000</v>
       </c>
       <c r="I21" s="3">
-        <v>9863000</v>
+        <v>9898000</v>
       </c>
       <c r="J21" s="3">
-        <v>10298000</v>
+        <v>10079000</v>
       </c>
       <c r="K21" s="3">
         <v>9530000</v>
@@ -1285,7 +1285,7 @@
         <v>2207000</v>
       </c>
       <c r="G22" s="3">
-        <v>4259000</v>
+        <v>2097000</v>
       </c>
       <c r="H22" s="3">
         <v>2204000</v>
@@ -1381,10 +1381,10 @@
         <v>519000</v>
       </c>
       <c r="I24" s="3">
-        <v>428000</v>
+        <v>448000</v>
       </c>
       <c r="J24" s="3">
-        <v>1308000</v>
+        <v>1196000</v>
       </c>
       <c r="K24" s="3">
         <v>1156000</v>
@@ -1471,10 +1471,10 @@
         <v>3578000</v>
       </c>
       <c r="I26" s="3">
-        <v>2645000</v>
+        <v>2625000</v>
       </c>
       <c r="J26" s="3">
-        <v>2958000</v>
+        <v>3070000</v>
       </c>
       <c r="K26" s="3">
         <v>2578000</v>
@@ -1501,25 +1501,25 @@
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4190000</v>
+        <v>2729000</v>
       </c>
       <c r="E27" s="3">
-        <v>3767000</v>
+        <v>2442000</v>
       </c>
       <c r="F27" s="3">
-        <v>3946000</v>
+        <v>3799000</v>
       </c>
       <c r="G27" s="3">
-        <v>1277000</v>
+        <v>1269000</v>
       </c>
       <c r="H27" s="3">
-        <v>3714000</v>
+        <v>3687000</v>
       </c>
       <c r="I27" s="3">
-        <v>2667000</v>
+        <v>2661000</v>
       </c>
       <c r="J27" s="3">
-        <v>2953000</v>
+        <v>3053000</v>
       </c>
       <c r="K27" s="3">
         <v>2560000</v>
@@ -1606,10 +1606,10 @@
         <v>-7000</v>
       </c>
       <c r="I29" s="3">
-        <v>-1000</v>
+        <v>19000</v>
       </c>
       <c r="J29" s="3">
-        <v>106000</v>
+        <v>-6000</v>
       </c>
       <c r="K29" s="3">
         <v>-408000</v>
@@ -1726,25 +1726,25 @@
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>-711000</v>
+        <v>682000</v>
       </c>
       <c r="E32" s="3">
-        <v>-505000</v>
+        <v>478000</v>
       </c>
       <c r="F32" s="3">
-        <v>-698000</v>
+        <v>685000</v>
       </c>
       <c r="G32" s="3">
-        <v>-608000</v>
+        <v>-1584000</v>
       </c>
       <c r="H32" s="3">
-        <v>-592000</v>
+        <v>561000</v>
       </c>
       <c r="I32" s="3">
-        <v>-482000</v>
+        <v>462000</v>
       </c>
       <c r="J32" s="3">
-        <v>-627000</v>
+        <v>614000</v>
       </c>
       <c r="K32" s="3">
         <v>-448000</v>
@@ -1771,19 +1771,19 @@
         <v>28</v>
       </c>
       <c r="D33" s="3">
-        <v>2735000</v>
+        <v>2841000</v>
       </c>
       <c r="E33" s="3">
-        <v>2444000</v>
+        <v>2550000</v>
       </c>
       <c r="F33" s="3">
-        <v>3802000</v>
+        <v>3908000</v>
       </c>
       <c r="G33" s="3">
-        <v>1270000</v>
+        <v>1377000</v>
       </c>
       <c r="H33" s="3">
-        <v>3707000</v>
+        <v>3748000</v>
       </c>
       <c r="I33" s="3">
         <v>2666000</v>
@@ -1861,19 +1861,19 @@
         <v>30</v>
       </c>
       <c r="D35" s="3">
-        <v>2735000</v>
+        <v>2841000</v>
       </c>
       <c r="E35" s="3">
-        <v>2444000</v>
+        <v>2550000</v>
       </c>
       <c r="F35" s="3">
-        <v>3802000</v>
+        <v>3908000</v>
       </c>
       <c r="G35" s="3">
-        <v>1270000</v>
+        <v>1377000</v>
       </c>
       <c r="H35" s="3">
-        <v>3707000</v>
+        <v>3748000</v>
       </c>
       <c r="I35" s="3">
         <v>2666000</v>
@@ -2000,7 +2000,7 @@
         <v>409000</v>
       </c>
       <c r="F41" s="3">
-        <v>343000</v>
+        <v>341000</v>
       </c>
       <c r="G41" s="3">
         <v>259000</v>
@@ -2038,26 +2038,26 @@
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G42" s="3" t="s">
-        <v>8</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
+        <v>18000</v>
       </c>
       <c r="H42" s="3">
-        <v>18000</v>
+        <v>6000</v>
       </c>
       <c r="I42" s="3">
-        <v>37000</v>
+        <v>0</v>
       </c>
       <c r="J42" s="3">
-        <v>35000</v>
+        <v>1000</v>
       </c>
       <c r="K42" s="3">
         <v>111000</v>
@@ -2090,7 +2090,7 @@
         <v>4415000</v>
       </c>
       <c r="F43" s="3">
-        <v>3610000</v>
+        <v>3522000</v>
       </c>
       <c r="G43" s="3">
         <v>3153000</v>
@@ -2099,10 +2099,10 @@
         <v>3060000</v>
       </c>
       <c r="I43" s="3">
-        <v>3134000</v>
+        <v>3863000</v>
       </c>
       <c r="J43" s="3">
-        <v>2774000</v>
+        <v>3104000</v>
       </c>
       <c r="K43" s="3">
         <v>2644000</v>
@@ -2135,7 +2135,7 @@
         <v>3584000</v>
       </c>
       <c r="F44" s="3">
-        <v>3199000</v>
+        <v>3111000</v>
       </c>
       <c r="G44" s="3">
         <v>3167000</v>
@@ -2174,25 +2174,25 @@
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>4093000</v>
+        <v>4017000</v>
       </c>
       <c r="E45" s="3">
-        <v>4814000</v>
+        <v>4732000</v>
       </c>
       <c r="F45" s="3">
-        <v>2788000</v>
+        <v>2796000</v>
       </c>
       <c r="G45" s="3">
-        <v>2103000</v>
+        <v>1891000</v>
       </c>
       <c r="H45" s="3">
-        <v>2542000</v>
+        <v>2332000</v>
       </c>
       <c r="I45" s="3">
-        <v>3017000</v>
+        <v>2184000</v>
       </c>
       <c r="J45" s="3">
-        <v>2036000</v>
+        <v>1602000</v>
       </c>
       <c r="K45" s="3">
         <v>1370000</v>
@@ -2270,19 +2270,19 @@
         <v>455000</v>
       </c>
       <c r="F47" s="3">
-        <v>970000</v>
+        <v>457000</v>
       </c>
       <c r="G47" s="3">
-        <v>961000</v>
+        <v>1519000</v>
       </c>
       <c r="H47" s="3">
-        <v>1937000</v>
+        <v>2368000</v>
       </c>
       <c r="I47" s="3">
-        <v>1413000</v>
+        <v>1778000</v>
       </c>
       <c r="J47" s="3">
-        <v>1191000</v>
+        <v>1553000</v>
       </c>
       <c r="K47" s="3">
         <v>976000</v>
@@ -2309,25 +2309,25 @@
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>116407000</v>
+        <v>114897000</v>
       </c>
       <c r="E48" s="3">
-        <v>225571000</v>
+        <v>111392000</v>
       </c>
       <c r="F48" s="3">
-        <v>112674000</v>
+        <v>105290000</v>
       </c>
       <c r="G48" s="3">
-        <v>108306000</v>
+        <v>106854000</v>
       </c>
       <c r="H48" s="3">
-        <v>103785000</v>
+        <v>102339000</v>
       </c>
       <c r="I48" s="3">
-        <v>91694000</v>
+        <v>90181000</v>
       </c>
       <c r="J48" s="3">
-        <v>86391000</v>
+        <v>84824000</v>
       </c>
       <c r="K48" s="3">
         <v>82520000</v>
@@ -2357,22 +2357,22 @@
         <v>19303000</v>
       </c>
       <c r="E49" s="3">
-        <v>38606000</v>
+        <v>19303000</v>
       </c>
       <c r="F49" s="3">
-        <v>19303000</v>
+        <v>19539000</v>
       </c>
       <c r="G49" s="3">
-        <v>19303000</v>
+        <v>19598000</v>
       </c>
       <c r="H49" s="3">
-        <v>19303000</v>
+        <v>19552000</v>
       </c>
       <c r="I49" s="3">
-        <v>19303000</v>
+        <v>19549000</v>
       </c>
       <c r="J49" s="3">
-        <v>19396000</v>
+        <v>19626000</v>
       </c>
       <c r="K49" s="3">
         <v>19425000</v>
@@ -2489,25 +2489,25 @@
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>27922000</v>
+        <v>15814000</v>
       </c>
       <c r="E52" s="3">
-        <v>32316000</v>
+        <v>19069000</v>
       </c>
       <c r="F52" s="3">
-        <v>26700000</v>
+        <v>21874000</v>
       </c>
       <c r="G52" s="3">
-        <v>25136000</v>
+        <v>13314000</v>
       </c>
       <c r="H52" s="3">
-        <v>24650000</v>
+        <v>12194000</v>
       </c>
       <c r="I52" s="3">
-        <v>23268000</v>
+        <v>10553000</v>
       </c>
       <c r="J52" s="3">
-        <v>22483000</v>
+        <v>11016000</v>
       </c>
       <c r="K52" s="3">
         <v>21801000</v>
@@ -2668,7 +2668,7 @@
         <v>4754000</v>
       </c>
       <c r="F57" s="3">
-        <v>3629000</v>
+        <v>3531000</v>
       </c>
       <c r="G57" s="3">
         <v>3144000</v>
@@ -2707,19 +2707,19 @@
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>7088000</v>
+        <v>7276000</v>
       </c>
       <c r="E58" s="3">
-        <v>11984000</v>
+        <v>8009000</v>
       </c>
       <c r="F58" s="3">
-        <v>6691000</v>
+        <v>6875000</v>
       </c>
       <c r="G58" s="3">
-        <v>7111000</v>
+        <v>7288000</v>
       </c>
       <c r="H58" s="3">
-        <v>6276000</v>
+        <v>6484000</v>
       </c>
       <c r="I58" s="3">
         <v>6816000</v>
@@ -2752,25 +2752,25 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>5967000</v>
+        <v>5034000</v>
       </c>
       <c r="E59" s="3">
-        <v>8456000</v>
+        <v>5484000</v>
       </c>
       <c r="F59" s="3">
-        <v>5611000</v>
+        <v>4071000</v>
       </c>
       <c r="G59" s="3">
-        <v>6050000</v>
+        <v>3210000</v>
       </c>
       <c r="H59" s="3">
-        <v>4989000</v>
+        <v>2741000</v>
       </c>
       <c r="I59" s="3">
-        <v>4738000</v>
+        <v>3378000</v>
       </c>
       <c r="J59" s="3">
-        <v>4032000</v>
+        <v>2691000</v>
       </c>
       <c r="K59" s="3">
         <v>3751000</v>
@@ -2842,19 +2842,19 @@
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>72452000</v>
+        <v>73369000</v>
       </c>
       <c r="E61" s="3">
-        <v>65873000</v>
+        <v>66749000</v>
       </c>
       <c r="F61" s="3">
-        <v>60448000</v>
+        <v>61388000</v>
       </c>
       <c r="G61" s="3">
-        <v>55625000</v>
+        <v>56965000</v>
       </c>
       <c r="H61" s="3">
-        <v>54985000</v>
+        <v>56417000</v>
       </c>
       <c r="I61" s="3">
         <v>51123000</v>
@@ -2887,25 +2887,25 @@
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>36814000</v>
+        <v>24149000</v>
       </c>
       <c r="E62" s="3">
-        <v>39560000</v>
+        <v>28966000</v>
       </c>
       <c r="F62" s="3">
-        <v>42072000</v>
+        <v>30065000</v>
       </c>
       <c r="G62" s="3">
-        <v>41274000</v>
+        <v>29034000</v>
       </c>
       <c r="H62" s="3">
-        <v>41150000</v>
+        <v>29282000</v>
       </c>
       <c r="I62" s="3">
-        <v>35394000</v>
+        <v>26032000</v>
       </c>
       <c r="J62" s="3">
-        <v>34660000</v>
+        <v>26397000</v>
       </c>
       <c r="K62" s="3">
         <v>34593000</v>
@@ -3067,25 +3067,25 @@
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>127781000</v>
+        <v>126706000</v>
       </c>
       <c r="E66" s="3">
-        <v>128764000</v>
+        <v>126233000</v>
       </c>
       <c r="F66" s="3">
-        <v>120291000</v>
+        <v>118451000</v>
       </c>
       <c r="G66" s="3">
-        <v>114424000</v>
+        <v>113204000</v>
       </c>
       <c r="H66" s="3">
-        <v>112016000</v>
+        <v>110887000</v>
       </c>
       <c r="I66" s="3">
-        <v>101575000</v>
+        <v>101558000</v>
       </c>
       <c r="J66" s="3">
-        <v>96175000</v>
+        <v>96177000</v>
       </c>
       <c r="K66" s="3">
         <v>91728000</v>
@@ -3631,19 +3631,19 @@
         <v>28</v>
       </c>
       <c r="D81" s="3">
-        <v>2735000</v>
+        <v>2841000</v>
       </c>
       <c r="E81" s="3">
-        <v>2444000</v>
+        <v>2550000</v>
       </c>
       <c r="F81" s="3">
-        <v>3802000</v>
+        <v>3908000</v>
       </c>
       <c r="G81" s="3">
-        <v>1270000</v>
+        <v>1377000</v>
       </c>
       <c r="H81" s="3">
-        <v>3707000</v>
+        <v>3748000</v>
       </c>
       <c r="I81" s="3">
         <v>2666000</v>
@@ -3695,10 +3695,10 @@
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>6084000</v>
+        <v>5561000</v>
       </c>
       <c r="E83" s="3">
-        <v>5843000</v>
+        <v>5342000</v>
       </c>
       <c r="F83" s="3">
         <v>5663000</v>
@@ -4228,25 +4228,25 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3244000</v>
+        <v>3138000</v>
       </c>
       <c r="E96" s="3">
-        <v>-3179000</v>
+        <v>3073000</v>
       </c>
       <c r="F96" s="3">
-        <v>-3114000</v>
+        <v>3008000</v>
       </c>
       <c r="G96" s="3">
-        <v>-2812000</v>
+        <v>0</v>
       </c>
       <c r="H96" s="3">
-        <v>-2668000</v>
+        <v>0</v>
       </c>
       <c r="I96" s="3">
-        <v>-2471000</v>
+        <v>2471000</v>
       </c>
       <c r="J96" s="3">
-        <v>-2450000</v>
+        <v>2450000</v>
       </c>
       <c r="K96" s="3">
         <v>-2332000</v>
@@ -4452,26 +4452,26 @@
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>

--- a/AAII_Financials/Yearly/DUK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DUK_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
   <si>
     <t>DUK</t>
   </si>
@@ -656,208 +656,220 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:Q102"/>
+  <dimension ref="A5:R102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="15" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>44926</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44561</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44196</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>43830</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43465</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43100</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>42735</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42369</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42004</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>41639</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41274</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>40908</v>
       </c>
-      <c r="Q7" s="2"/>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R7" s="2"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>29934000</v>
+      </c>
+      <c r="E8" s="3">
         <v>28602000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28319000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>24201000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>22951000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>24658000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>24116000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>23189000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>22743000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>22371000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>22509000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>22756000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>17912000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>14529000</v>
       </c>
-      <c r="Q8" s="3"/>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R8" s="3"/>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>14744000</v>
+        <v>14739000</v>
       </c>
       <c r="E9" s="3">
-        <v>15207000</v>
+        <v>14626000</v>
       </c>
       <c r="F9" s="3">
+        <v>15182000</v>
+      </c>
+      <c r="G9" s="3">
         <v>12132000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>11683000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>13082000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>13399000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>12486000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>13114000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13389000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13956000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13545000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>16817000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>8915000</v>
       </c>
-      <c r="Q9" s="3"/>
-    </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R9" s="3"/>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>13858000</v>
+        <v>15195000</v>
       </c>
       <c r="E10" s="3">
-        <v>13112000</v>
+        <v>13976000</v>
       </c>
       <c r="F10" s="3">
+        <v>13137000</v>
+      </c>
+      <c r="G10" s="3">
         <v>12069000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>11268000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>11576000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>10717000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10703000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>9629000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>8982000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8553000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>9211000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>1095000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>5614000</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R10" s="3"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -875,8 +887,9 @@
       <c r="O11" s="3"/>
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R11" s="3"/>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -919,9 +932,12 @@
       <c r="P12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q12" s="3"/>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R12" s="3"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -964,99 +980,108 @@
       <c r="P13" s="3">
         <v>0</v>
       </c>
-      <c r="Q13" s="3"/>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="Q13" s="3">
+        <v>0</v>
+      </c>
+      <c r="R13" s="3"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>135000</v>
+        <v>13000</v>
       </c>
       <c r="E14" s="3">
-        <v>548000</v>
+        <v>253000</v>
       </c>
       <c r="F14" s="3">
+        <v>573000</v>
+      </c>
+      <c r="G14" s="3">
         <v>469000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>882000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>12000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>677000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>313000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>-9000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>106000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>81000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>399000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>666000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>335000</v>
       </c>
-      <c r="Q14" s="3"/>
-    </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R14" s="3"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>5793000</v>
+      </c>
+      <c r="E15" s="3">
         <v>5253000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5086000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>4745000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4504000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4548000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4074000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>3527000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3294000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3053000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>2969000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2668000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2145000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>1806000</v>
       </c>
-      <c r="Q15" s="3"/>
-    </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.2">
+      <c r="R15" s="3"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1071,98 +1096,105 @@
       <c r="O16" s="3"/>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
-    </row>
-    <row r="17" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R16" s="3"/>
+    </row>
+    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>21397000</v>
+        <v>21998000</v>
       </c>
       <c r="E17" s="3">
-        <v>21759000</v>
+        <v>21279000</v>
       </c>
       <c r="F17" s="3">
+        <v>21734000</v>
+      </c>
+      <c r="G17" s="3">
         <v>18232000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>17498000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>18937000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>18754000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>17251000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17541000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17323000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17677000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17886000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>15011000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>11760000</v>
       </c>
-      <c r="Q17" s="3"/>
-    </row>
-    <row r="18" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R17" s="3"/>
+    </row>
+    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>7205000</v>
+        <v>7936000</v>
       </c>
       <c r="E18" s="3">
-        <v>6560000</v>
+        <v>7323000</v>
       </c>
       <c r="F18" s="3">
+        <v>6585000</v>
+      </c>
+      <c r="G18" s="3">
         <v>5969000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5453000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5721000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5362000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5938000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5202000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5048000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>4832000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4870000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>2901000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2769000</v>
       </c>
-      <c r="Q18" s="3"/>
-    </row>
-    <row r="19" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R18" s="3"/>
+    </row>
+    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1180,233 +1212,249 @@
       <c r="O19" s="3"/>
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
-    </row>
-    <row r="20" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R19" s="3"/>
+    </row>
+    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-592000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-682000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-478000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-685000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1584000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-561000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-462000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-614000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>448000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>389000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>460000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>254000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>577000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>555000</v>
       </c>
-      <c r="Q20" s="3"/>
-    </row>
-    <row r="21" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R20" s="3"/>
+    </row>
+    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>13140000</v>
+        <v>14321000</v>
       </c>
       <c r="E21" s="3">
-        <v>12124000</v>
+        <v>13258000</v>
       </c>
       <c r="F21" s="3">
+        <v>12149000</v>
+      </c>
+      <c r="G21" s="3">
         <v>11399000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>8373000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>10830000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>9898000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>10079000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>9530000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9050000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>8799000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8353000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>6130000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>5350000</v>
       </c>
-      <c r="Q21" s="3"/>
-    </row>
-    <row r="22" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R21" s="3"/>
+    </row>
+    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3384000</v>
+      </c>
+      <c r="E22" s="3">
         <v>3014000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>2439000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2207000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2097000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2204000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2094000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1986000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1916000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1527000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1529000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1329000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1244000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>859000</v>
       </c>
-      <c r="Q22" s="3"/>
-    </row>
-    <row r="23" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R22" s="3"/>
+    </row>
+    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5194000</v>
+      </c>
+      <c r="E23" s="3">
         <v>4767000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4078000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>3991000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>920000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>4097000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>3073000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>4266000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>3734000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3910000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3763000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3795000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>2234000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2465000</v>
       </c>
-      <c r="Q23" s="3"/>
-    </row>
-    <row r="24" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R23" s="3"/>
+    </row>
+    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>590000</v>
+      </c>
+      <c r="E24" s="3">
         <v>438000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>300000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>268000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>-169000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>519000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>448000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>1196000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1156000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1256000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1225000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1205000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>623000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>752000</v>
       </c>
-      <c r="Q24" s="3"/>
-    </row>
-    <row r="25" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R24" s="3"/>
+    </row>
+    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1449,99 +1497,108 @@
       <c r="P25" s="3">
         <v>0</v>
       </c>
-      <c r="Q25" s="3"/>
-    </row>
-    <row r="26" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q25" s="3">
+        <v>0</v>
+      </c>
+      <c r="R25" s="3"/>
+    </row>
+    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>4604000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4329000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>3778000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3723000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>1089000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>3578000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>2625000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>3070000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>2578000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2654000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2538000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2590000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>1611000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1713000</v>
       </c>
-      <c r="Q26" s="3"/>
-    </row>
-    <row r="27" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R26" s="3"/>
+    </row>
+    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>2729000</v>
+        <v>4402000</v>
       </c>
       <c r="E27" s="3">
-        <v>2442000</v>
+        <v>2735000</v>
       </c>
       <c r="F27" s="3">
+        <v>2444000</v>
+      </c>
+      <c r="G27" s="3">
         <v>3799000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>1269000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>3687000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>2661000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>3053000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>2560000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2639000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2532000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2579000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>1597000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1705000</v>
       </c>
-      <c r="Q27" s="3"/>
-    </row>
-    <row r="28" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R27" s="3"/>
+    </row>
+    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1584,54 +1641,60 @@
       <c r="P28" s="3">
         <v>0</v>
       </c>
-      <c r="Q28" s="3"/>
-    </row>
-    <row r="29" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q28" s="3">
+        <v>0</v>
+      </c>
+      <c r="R28" s="3"/>
+    </row>
+    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>10000</v>
+      </c>
+      <c r="E29" s="3">
         <v>-1455000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-1323000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-144000</v>
-      </c>
-      <c r="G29" s="3">
-        <v>-7000</v>
       </c>
       <c r="H29" s="3">
         <v>-7000</v>
       </c>
       <c r="I29" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="J29" s="3">
         <v>19000</v>
       </c>
-      <c r="J29" s="3">
+      <c r="K29" s="3">
         <v>-6000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-408000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>177000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>-649000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>86000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>207000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>1000</v>
       </c>
-      <c r="Q29" s="3"/>
-    </row>
-    <row r="30" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R29" s="3"/>
+    </row>
+    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1674,9 +1737,12 @@
       <c r="P30" s="3">
         <v>0</v>
       </c>
-      <c r="Q30" s="3"/>
-    </row>
-    <row r="31" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3"/>
+    </row>
+    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1719,99 +1785,108 @@
       <c r="P31" s="3">
         <v>0</v>
       </c>
-      <c r="Q31" s="3"/>
-    </row>
-    <row r="32" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q31" s="3">
+        <v>0</v>
+      </c>
+      <c r="R31" s="3"/>
+    </row>
+    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>592000</v>
+      </c>
+      <c r="E32" s="3">
         <v>682000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>478000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>685000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1584000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>561000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>462000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>614000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-448000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-389000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-460000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-254000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-577000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-555000</v>
       </c>
-      <c r="Q32" s="3"/>
-    </row>
-    <row r="33" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R32" s="3"/>
+    </row>
+    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4524000</v>
+      </c>
+      <c r="E33" s="3">
         <v>2841000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2550000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>3908000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>1377000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>3748000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>2666000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>3059000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>2152000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2816000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>1883000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>2665000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>1804000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1706000</v>
       </c>
-      <c r="Q33" s="3"/>
-    </row>
-    <row r="34" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R33" s="3"/>
+    </row>
+    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1854,104 +1929,113 @@
       <c r="P34" s="3">
         <v>0</v>
       </c>
-      <c r="Q34" s="3"/>
-    </row>
-    <row r="35" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q34" s="3">
+        <v>0</v>
+      </c>
+      <c r="R34" s="3"/>
+    </row>
+    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4524000</v>
+      </c>
+      <c r="E35" s="3">
         <v>2841000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2550000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>3908000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>1377000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>3748000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>2666000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>3059000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>2152000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2816000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>1883000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>2665000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>1804000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1706000</v>
       </c>
-      <c r="Q35" s="3"/>
-    </row>
-    <row r="37" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R35" s="3"/>
+    </row>
+    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>44926</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44561</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44196</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>43830</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43465</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43100</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>42735</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42369</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42004</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>41639</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41274</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>40908</v>
       </c>
-      <c r="Q38" s="2"/>
-    </row>
-    <row r="39" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R38" s="2"/>
+    </row>
+    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -1969,8 +2053,9 @@
       <c r="O39" s="3"/>
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
-    </row>
-    <row r="40" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R39" s="3"/>
+    </row>
+    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -1988,53 +2073,57 @@
       <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
-    </row>
-    <row r="41" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R40" s="3"/>
+    </row>
+    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>314000</v>
+      </c>
+      <c r="E41" s="3">
         <v>253000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>409000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>341000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>259000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>311000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>442000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>358000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>392000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>383000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>2036000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1501000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1424000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>2110000</v>
       </c>
-      <c r="Q41" s="3"/>
-    </row>
-    <row r="42" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R41" s="3"/>
+    </row>
+    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2048,308 +2137,329 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>18000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6000</v>
       </c>
-      <c r="I42" s="3">
-        <v>0</v>
-      </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>1000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>111000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>6000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>18000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>178000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>333000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>190000</v>
       </c>
-      <c r="Q42" s="3"/>
-    </row>
-    <row r="43" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R42" s="3"/>
+    </row>
+    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>4672000</v>
+      </c>
+      <c r="E43" s="3">
         <v>4131000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>4415000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>3522000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3153000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3060000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3863000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3104000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2644000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2263000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2764000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>3005000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2717000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1941000</v>
       </c>
-      <c r="Q43" s="3"/>
-    </row>
-    <row r="44" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R43" s="3"/>
+    </row>
+    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>4509000</v>
+      </c>
+      <c r="E44" s="3">
         <v>4292000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>3584000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3111000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3167000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3232000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3084000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3250000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3522000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3746000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3459000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>6500000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>3223000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1588000</v>
       </c>
-      <c r="Q44" s="3"/>
-    </row>
-    <row r="45" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R44" s="3"/>
+    </row>
+    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>3371000</v>
+      </c>
+      <c r="E45" s="3">
         <v>4017000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4732000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>2796000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>1891000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>2332000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2184000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>1602000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1370000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1924000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3662000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2734000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2425000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1051000</v>
       </c>
-      <c r="Q45" s="3"/>
-    </row>
-    <row r="46" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R45" s="3"/>
+    </row>
+    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>12950000</v>
+      </c>
+      <c r="E46" s="3">
         <v>12769000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>13222000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>9940000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>8682000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>9163000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9714000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>8453000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8039000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8322000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>11575000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>10516000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10122000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>6880000</v>
       </c>
-      <c r="Q46" s="3"/>
-    </row>
-    <row r="47" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R46" s="3"/>
+    </row>
+    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>353000</v>
+      </c>
+      <c r="E47" s="3">
         <v>492000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>455000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>457000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>1519000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2368000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>1778000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1553000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>976000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>506000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>3038000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>555000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>554000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>522000</v>
       </c>
-      <c r="Q47" s="3"/>
-    </row>
-    <row r="48" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R47" s="3"/>
+    </row>
+    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>122757000</v>
+      </c>
+      <c r="E48" s="3">
         <v>114897000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>111392000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>105290000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>106854000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>102339000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>90181000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>84824000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>82520000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>73779000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>70046000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>170639000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>68558000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>42661000</v>
       </c>
-      <c r="Q48" s="3"/>
-    </row>
-    <row r="49" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R48" s="3"/>
+    </row>
+    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
@@ -2360,41 +2470,44 @@
         <v>19303000</v>
       </c>
       <c r="F49" s="3">
+        <v>19303000</v>
+      </c>
+      <c r="G49" s="3">
         <v>19539000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>19598000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>19552000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>19549000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>19626000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>19425000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>16072000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>16321000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>32680000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>16737000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>4212000</v>
       </c>
-      <c r="Q49" s="3"/>
-    </row>
-    <row r="50" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R49" s="3"/>
+    </row>
+    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2437,9 +2550,12 @@
       <c r="P50" s="3">
         <v>0</v>
       </c>
-      <c r="Q50" s="3"/>
-    </row>
-    <row r="51" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q50" s="3">
+        <v>0</v>
+      </c>
+      <c r="R50" s="3"/>
+    </row>
+    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2482,54 +2598,60 @@
       <c r="P51" s="3">
         <v>0</v>
       </c>
-      <c r="Q51" s="3"/>
-    </row>
-    <row r="52" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q51" s="3">
+        <v>0</v>
+      </c>
+      <c r="R51" s="3"/>
+    </row>
+    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16726000</v>
+      </c>
+      <c r="E52" s="3">
         <v>15814000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>19069000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>21874000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13314000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12194000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10553000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>11016000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>21801000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>25562000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>25398000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>17878000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>17885000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8251000</v>
       </c>
-      <c r="Q52" s="3"/>
-    </row>
-    <row r="53" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R52" s="3"/>
+    </row>
+    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2572,54 +2694,60 @@
       <c r="P53" s="3">
         <v>0</v>
       </c>
-      <c r="Q53" s="3"/>
-    </row>
-    <row r="54" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q53" s="3">
+        <v>0</v>
+      </c>
+      <c r="R53" s="3"/>
+    </row>
+    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>186343000</v>
+      </c>
+      <c r="E54" s="3">
         <v>176893000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>178086000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>169587000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>162388000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>158838000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>145392000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>137914000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>132761000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>121156000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>120557000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>114779000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>113856000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>62526000</v>
       </c>
-      <c r="Q54" s="3"/>
-    </row>
-    <row r="55" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R54" s="3"/>
+    </row>
+    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2637,8 +2765,9 @@
       <c r="O55" s="3"/>
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
-    </row>
-    <row r="56" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R55" s="3"/>
+    </row>
+    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2656,278 +2785,297 @@
       <c r="O56" s="3"/>
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
-    </row>
-    <row r="57" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R56" s="3"/>
+    </row>
+    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>5479000</v>
+      </c>
+      <c r="E57" s="3">
         <v>4228000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>4754000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>3531000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3144000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>3487000</v>
       </c>
       <c r="I57" s="3">
         <v>3487000</v>
       </c>
       <c r="J57" s="3">
+        <v>3487000</v>
+      </c>
+      <c r="K57" s="3">
         <v>3043000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>2994000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2350000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2271000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2391000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2444000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1433000</v>
       </c>
-      <c r="Q57" s="3"/>
-    </row>
-    <row r="58" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R57" s="3"/>
+    </row>
+    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8141000</v>
+      </c>
+      <c r="E58" s="3">
         <v>7276000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>8009000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>6875000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>7288000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6484000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6816000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>5407000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>4806000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>5659000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5321000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>2943000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>4167000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>2321000</v>
       </c>
-      <c r="Q58" s="3"/>
-    </row>
-    <row r="59" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R58" s="3"/>
+    </row>
+    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>4882000</v>
+      </c>
+      <c r="E59" s="3">
         <v>5034000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>5484000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>4071000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>3210000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>2741000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>3378000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>2691000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>3751000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>5506000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>6091000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>3617000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3418000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1774000</v>
       </c>
-      <c r="Q59" s="3"/>
-    </row>
-    <row r="60" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R59" s="3"/>
+    </row>
+    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>19357000</v>
+      </c>
+      <c r="E60" s="3">
         <v>17283000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>18873000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>15931000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>16305000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>14752000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>15041000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>12482000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>11551000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11400000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11233000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>8644000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>10029000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>5528000</v>
       </c>
-      <c r="Q60" s="3"/>
-    </row>
-    <row r="61" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R60" s="3"/>
+    </row>
+    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>77297000</v>
+      </c>
+      <c r="E61" s="3">
         <v>73369000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>66749000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>61388000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>56965000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>56417000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>51123000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>49035000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>45576000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>36842000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>37061000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>38152000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>36351000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>18679000</v>
       </c>
-      <c r="Q61" s="3"/>
-    </row>
-    <row r="62" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R61" s="3"/>
+    </row>
+    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>25681000</v>
+      </c>
+      <c r="E62" s="3">
         <v>24149000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>28966000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>30065000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>29034000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>29282000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>26032000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>26397000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>34593000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>33949000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>33004000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>26664000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>26535000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>15454000</v>
       </c>
-      <c r="Q62" s="3"/>
-    </row>
-    <row r="63" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R62" s="3"/>
+    </row>
+    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -2970,9 +3118,12 @@
       <c r="P63" s="3">
         <v>0</v>
       </c>
-      <c r="Q63" s="3"/>
-    </row>
-    <row r="64" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q63" s="3">
+        <v>0</v>
+      </c>
+      <c r="R63" s="3"/>
+    </row>
+    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3015,9 +3166,12 @@
       <c r="P64" s="3">
         <v>0</v>
       </c>
-      <c r="Q64" s="3"/>
-    </row>
-    <row r="65" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q64" s="3">
+        <v>0</v>
+      </c>
+      <c r="R64" s="3"/>
+    </row>
+    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3060,54 +3214,60 @@
       <c r="P65" s="3">
         <v>0</v>
       </c>
-      <c r="Q65" s="3"/>
-    </row>
-    <row r="66" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q65" s="3">
+        <v>0</v>
+      </c>
+      <c r="R65" s="3"/>
+    </row>
+    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>135087000</v>
+      </c>
+      <c r="E66" s="3">
         <v>126706000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>126233000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>118451000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>113204000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>110887000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>101558000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>96177000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>91728000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>81429000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>79682000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>73449000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>72993000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>39754000</v>
       </c>
-      <c r="Q66" s="3"/>
-    </row>
-    <row r="67" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R66" s="3"/>
+    </row>
+    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3125,8 +3285,9 @@
       <c r="O67" s="3"/>
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
-    </row>
-    <row r="68" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R67" s="3"/>
+    </row>
+    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3169,9 +3330,12 @@
       <c r="P68" s="3">
         <v>0</v>
       </c>
-      <c r="Q68" s="3"/>
-    </row>
-    <row r="69" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q68" s="3">
+        <v>0</v>
+      </c>
+      <c r="R68" s="3"/>
+    </row>
+    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3214,14 +3378,17 @@
       <c r="P69" s="3">
         <v>0</v>
       </c>
-      <c r="Q69" s="3"/>
-    </row>
-    <row r="70" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q69" s="3">
+        <v>0</v>
+      </c>
+      <c r="R69" s="3"/>
+    </row>
+    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
       <c r="D70" s="3">
-        <v>1962000</v>
+        <v>973000</v>
       </c>
       <c r="E70" s="3">
         <v>1962000</v>
@@ -3236,7 +3403,7 @@
         <v>1962000</v>
       </c>
       <c r="I70" s="3">
-        <v>0</v>
+        <v>1962000</v>
       </c>
       <c r="J70" s="3">
         <v>0</v>
@@ -3259,9 +3426,12 @@
       <c r="P70" s="3">
         <v>0</v>
       </c>
-      <c r="Q70" s="3"/>
-    </row>
-    <row r="71" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q70" s="3">
+        <v>0</v>
+      </c>
+      <c r="R70" s="3"/>
+    </row>
+    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3304,54 +3474,60 @@
       <c r="P71" s="3">
         <v>0</v>
       </c>
-      <c r="Q71" s="3"/>
-    </row>
-    <row r="72" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q71" s="3">
+        <v>0</v>
+      </c>
+      <c r="R71" s="3"/>
+    </row>
+    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>3431000</v>
+      </c>
+      <c r="E72" s="3">
         <v>2235000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2637000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>3265000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2471000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>4108000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>3113000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3013000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2384000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2564000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2012000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2363000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1889000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1873000</v>
       </c>
-      <c r="Q72" s="3"/>
-    </row>
-    <row r="73" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R72" s="3"/>
+    </row>
+    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3394,9 +3570,12 @@
       <c r="P73" s="3">
         <v>0</v>
       </c>
-      <c r="Q73" s="3"/>
-    </row>
-    <row r="74" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q73" s="3">
+        <v>0</v>
+      </c>
+      <c r="R73" s="3"/>
+    </row>
+    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3439,9 +3618,12 @@
       <c r="P74" s="3">
         <v>0</v>
       </c>
-      <c r="Q74" s="3"/>
-    </row>
-    <row r="75" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q74" s="3">
+        <v>0</v>
+      </c>
+      <c r="R74" s="3"/>
+    </row>
+    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3484,54 +3666,60 @@
       <c r="P75" s="3">
         <v>0</v>
       </c>
-      <c r="Q75" s="3"/>
-    </row>
-    <row r="76" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q75" s="3">
+        <v>0</v>
+      </c>
+      <c r="R75" s="3"/>
+    </row>
+    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>49154000</v>
+      </c>
+      <c r="E76" s="3">
         <v>47150000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>47360000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>47334000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>46002000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>44860000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>43817000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>41739000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>41033000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>39727000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>40875000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>41330000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>40863000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>22772000</v>
       </c>
-      <c r="Q76" s="3"/>
-    </row>
-    <row r="77" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="R76" s="3"/>
+    </row>
+    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3574,104 +3762,113 @@
       <c r="P77" s="3">
         <v>0</v>
       </c>
-      <c r="Q77" s="3"/>
-    </row>
-    <row r="79" spans="2:17" x14ac:dyDescent="0.2">
+      <c r="Q77" s="3">
+        <v>0</v>
+      </c>
+      <c r="R77" s="3"/>
+    </row>
+    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:17" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>44926</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44561</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44196</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>43830</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43465</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43100</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>42735</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42369</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42004</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>41639</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41274</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>40908</v>
       </c>
-      <c r="Q80" s="2"/>
-    </row>
-    <row r="81" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R80" s="2"/>
+    </row>
+    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4524000</v>
+      </c>
+      <c r="E81" s="3">
         <v>2841000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2550000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>3908000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>1377000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>3748000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>2666000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>3059000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>2152000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2816000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>1883000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>2665000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>1804000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1706000</v>
       </c>
-      <c r="Q81" s="3"/>
-    </row>
-    <row r="82" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R81" s="3"/>
+    </row>
+    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3689,53 +3886,57 @@
       <c r="O82" s="3"/>
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
-    </row>
-    <row r="83" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R82" s="3"/>
+    </row>
+    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>5985000</v>
+      </c>
+      <c r="E83" s="3">
         <v>5561000</v>
       </c>
-      <c r="E83" s="3">
-        <v>5342000</v>
-      </c>
       <c r="F83" s="3">
+        <v>5843000</v>
+      </c>
+      <c r="G83" s="3">
         <v>5663000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5486000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5176000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>4696000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4046000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>3880000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3613000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3507000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3229000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>2652000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2026000</v>
       </c>
-      <c r="Q83" s="3"/>
-    </row>
-    <row r="84" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R83" s="3"/>
+    </row>
+    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3778,9 +3979,12 @@
       <c r="P84" s="3">
         <v>0</v>
       </c>
-      <c r="Q84" s="3"/>
-    </row>
-    <row r="85" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q84" s="3">
+        <v>0</v>
+      </c>
+      <c r="R84" s="3"/>
+    </row>
+    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -3823,9 +4027,12 @@
       <c r="P85" s="3">
         <v>0</v>
       </c>
-      <c r="Q85" s="3"/>
-    </row>
-    <row r="86" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q85" s="3">
+        <v>0</v>
+      </c>
+      <c r="R85" s="3"/>
+    </row>
+    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -3868,9 +4075,12 @@
       <c r="P86" s="3">
         <v>0</v>
       </c>
-      <c r="Q86" s="3"/>
-    </row>
-    <row r="87" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q86" s="3">
+        <v>0</v>
+      </c>
+      <c r="R86" s="3"/>
+    </row>
+    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -3913,9 +4123,12 @@
       <c r="P87" s="3">
         <v>0</v>
       </c>
-      <c r="Q87" s="3"/>
-    </row>
-    <row r="88" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q87" s="3">
+        <v>0</v>
+      </c>
+      <c r="R87" s="3"/>
+    </row>
+    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -3958,54 +4171,60 @@
       <c r="P88" s="3">
         <v>0</v>
       </c>
-      <c r="Q88" s="3"/>
-    </row>
-    <row r="89" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q88" s="3">
+        <v>0</v>
+      </c>
+      <c r="R88" s="3"/>
+    </row>
+    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12328000</v>
+      </c>
+      <c r="E89" s="3">
         <v>9878000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>5927000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>8290000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8856000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8209000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>7186000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>6624000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>7337000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7775000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>6038000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6382000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>5244000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>3672000</v>
       </c>
-      <c r="Q89" s="3"/>
-    </row>
-    <row r="90" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R89" s="3"/>
+    </row>
+    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4023,53 +4242,57 @@
       <c r="O90" s="3"/>
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
-    </row>
-    <row r="91" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R90" s="3"/>
+    </row>
+    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-12280000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12604000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11367000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9715000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9907000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11122000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9389000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-8052000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7901000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-6766000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-5384000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5526000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5501000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4363000</v>
       </c>
-      <c r="Q91" s="3"/>
-    </row>
-    <row r="92" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R91" s="3"/>
+    </row>
+    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4112,9 +4335,12 @@
       <c r="P92" s="3">
         <v>0</v>
       </c>
-      <c r="Q92" s="3"/>
-    </row>
-    <row r="93" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q92" s="3">
+        <v>0</v>
+      </c>
+      <c r="R92" s="3"/>
+    </row>
+    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4157,54 +4383,60 @@
       <c r="P93" s="3">
         <v>0</v>
       </c>
-      <c r="Q93" s="3"/>
-    </row>
-    <row r="94" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q93" s="3">
+        <v>0</v>
+      </c>
+      <c r="R93" s="3"/>
+    </row>
+    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-13123000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12475000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-11973000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10935000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10604000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11957000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10060000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8442000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11528000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5277000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5373000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-4978000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-6197000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-4434000</v>
       </c>
-      <c r="Q94" s="3"/>
-    </row>
-    <row r="95" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R94" s="3"/>
+    </row>
+    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4222,53 +4454,57 @@
       <c r="O95" s="3"/>
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
-    </row>
-    <row r="96" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R95" s="3"/>
+    </row>
+    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>3213000</v>
+      </c>
+      <c r="E96" s="3">
         <v>3138000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>3073000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3008000</v>
       </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
       <c r="H96" s="3">
         <v>0</v>
       </c>
       <c r="I96" s="3">
+        <v>0</v>
+      </c>
+      <c r="J96" s="3">
         <v>2471000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>2450000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>-2332000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2254000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2234000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2188000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-1752000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1329000</v>
       </c>
-      <c r="Q96" s="3"/>
-    </row>
-    <row r="97" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R96" s="3"/>
+    </row>
+    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4311,9 +4547,12 @@
       <c r="P97" s="3">
         <v>0</v>
       </c>
-      <c r="Q97" s="3"/>
-    </row>
-    <row r="98" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q97" s="3">
+        <v>0</v>
+      </c>
+      <c r="R97" s="3"/>
+    </row>
+    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4356,9 +4595,12 @@
       <c r="P98" s="3">
         <v>0</v>
       </c>
-      <c r="Q98" s="3"/>
-    </row>
-    <row r="99" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q98" s="3">
+        <v>0</v>
+      </c>
+      <c r="R98" s="3"/>
+    </row>
+    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4401,54 +4643,60 @@
       <c r="P99" s="3">
         <v>0</v>
       </c>
-      <c r="Q99" s="3"/>
-    </row>
-    <row r="100" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q99" s="3">
+        <v>0</v>
+      </c>
+      <c r="R99" s="3"/>
+    </row>
+    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>859000</v>
+      </c>
+      <c r="E100" s="3">
         <v>2351000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6129000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>2609000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>1731000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>3730000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>2960000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>1782000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>4251000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-2578000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-678000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1327000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>267000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1202000</v>
       </c>
-      <c r="Q100" s="3"/>
-    </row>
-    <row r="101" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="R100" s="3"/>
+    </row>
+    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4473,8 +4721,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -4491,52 +4739,58 @@
       <c r="P101" s="3">
         <v>0</v>
       </c>
-      <c r="Q101" s="3"/>
-    </row>
-    <row r="102" spans="3:17" x14ac:dyDescent="0.2">
+      <c r="Q101" s="3">
+        <v>0</v>
+      </c>
+      <c r="R101" s="3"/>
+    </row>
+    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>64000</v>
+      </c>
+      <c r="E102" s="3">
         <v>-246000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>83000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-36000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-17000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-18000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>86000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-36000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>60000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-80000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-13000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>77000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-686000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>440000</v>
       </c>
-      <c r="Q102" s="3"/>
+      <c r="R102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/AAII_Financials/Yearly/DUK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DUK_YR_FIN.xlsx
@@ -4461,7 +4461,7 @@
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>3213000</v>
+        <v>0</v>
       </c>
       <c r="E96" s="3">
         <v>3138000</v>

--- a/AAII_Financials/Yearly/DUK_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/DUK_YR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="117" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="119" uniqueCount="92">
   <si>
     <t>DUK</t>
   </si>
@@ -656,220 +656,232 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:R102"/>
+  <dimension ref="A5:S102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.28515625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="16" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="17" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>44926</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44561</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44196</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>43830</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>43465</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>43100</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>42735</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>42369</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>42004</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>41639</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>41274</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>40908</v>
       </c>
-      <c r="R7" s="2"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S7" s="2"/>
+    </row>
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>31790000</v>
+      </c>
+      <c r="E8" s="3">
         <v>29934000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>28602000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>28319000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>24201000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>22951000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>24658000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>24116000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>23189000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>22743000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>22371000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>22509000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>22756000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>17912000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>14529000</v>
       </c>
-      <c r="R8" s="3"/>
-    </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S8" s="3"/>
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
-        <v>14739000</v>
+        <v>15292000</v>
       </c>
       <c r="E9" s="3">
-        <v>14626000</v>
+        <v>14713000</v>
       </c>
       <c r="F9" s="3">
+        <v>14728000</v>
+      </c>
+      <c r="G9" s="3">
         <v>15182000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>12132000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>11683000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>13082000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>13399000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>12486000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>13114000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>13389000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>13956000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>13545000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>16817000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>8915000</v>
       </c>
-      <c r="R9" s="3"/>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S9" s="3"/>
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
-        <v>15195000</v>
+        <v>16498000</v>
       </c>
       <c r="E10" s="3">
-        <v>13976000</v>
+        <v>15221000</v>
       </c>
       <c r="F10" s="3">
+        <v>13874000</v>
+      </c>
+      <c r="G10" s="3">
         <v>13137000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>12069000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>11268000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>11576000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>10717000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>10703000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>9629000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>8982000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>8553000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>9211000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>1095000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>5614000</v>
       </c>
-      <c r="R10" s="3"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S10" s="3"/>
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -888,8 +900,9 @@
       <c r="P11" s="3"/>
       <c r="Q11" s="3"/>
       <c r="R11" s="3"/>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S11" s="3"/>
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -935,9 +948,12 @@
       <c r="Q12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R12" s="3"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="S12" s="3"/>
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -983,105 +999,114 @@
       <c r="Q13" s="3">
         <v>0</v>
       </c>
-      <c r="R13" s="3"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="R13" s="3">
+        <v>0</v>
+      </c>
+      <c r="S13" s="3"/>
+    </row>
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>13000</v>
+        <v>-49000</v>
       </c>
       <c r="E14" s="3">
-        <v>253000</v>
+        <v>39000</v>
       </c>
       <c r="F14" s="3">
+        <v>151000</v>
+      </c>
+      <c r="G14" s="3">
         <v>573000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>469000</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>882000</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>12000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>677000</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>313000</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>-9000</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>106000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>81000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>399000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>666000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>335000</v>
       </c>
-      <c r="R14" s="3"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S14" s="3"/>
+    </row>
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>6324000</v>
+      </c>
+      <c r="E15" s="3">
         <v>5793000</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>5253000</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>5086000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>4745000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>4504000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>4548000</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>4074000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>3527000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>3294000</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>3053000</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>2969000</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>2668000</v>
       </c>
-      <c r="P15" s="3">
+      <c r="Q15" s="3">
         <v>2145000</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="R15" s="3">
         <v>1806000</v>
       </c>
-      <c r="R15" s="3"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.2">
+      <c r="S15" s="3"/>
+    </row>
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1097,104 +1122,111 @@
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
-    </row>
-    <row r="17" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S16" s="3"/>
+    </row>
+    <row r="17" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>21998000</v>
+        <v>23213000</v>
       </c>
       <c r="E17" s="3">
-        <v>21279000</v>
+        <v>21972000</v>
       </c>
       <c r="F17" s="3">
+        <v>21381000</v>
+      </c>
+      <c r="G17" s="3">
         <v>21734000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>18232000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>17498000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>18937000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>18754000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>17251000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>17541000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>17323000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>17677000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>17886000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>15011000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>11760000</v>
       </c>
-      <c r="R17" s="3"/>
-    </row>
-    <row r="18" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S17" s="3"/>
+    </row>
+    <row r="18" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>7936000</v>
+        <v>8577000</v>
       </c>
       <c r="E18" s="3">
-        <v>7323000</v>
+        <v>7962000</v>
       </c>
       <c r="F18" s="3">
+        <v>7221000</v>
+      </c>
+      <c r="G18" s="3">
         <v>6585000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>5969000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>5453000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>5721000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>5362000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>5938000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>5202000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>5048000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>4832000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>4870000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>2901000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>2769000</v>
       </c>
-      <c r="R18" s="3"/>
-    </row>
-    <row r="19" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S18" s="3"/>
+    </row>
+    <row r="19" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1213,248 +1245,264 @@
       <c r="P19" s="3"/>
       <c r="Q19" s="3"/>
       <c r="R19" s="3"/>
-    </row>
-    <row r="20" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S19" s="3"/>
+    </row>
+    <row r="20" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-669000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-592000</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-682000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-478000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-685000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1584000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-561000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-462000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-614000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>448000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>389000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>460000</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>254000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>577000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>555000</v>
       </c>
-      <c r="R20" s="3"/>
-    </row>
-    <row r="21" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S20" s="3"/>
+    </row>
+    <row r="21" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>14321000</v>
+        <v>15570000</v>
       </c>
       <c r="E21" s="3">
-        <v>13258000</v>
+        <v>14347000</v>
       </c>
       <c r="F21" s="3">
+        <v>13156000</v>
+      </c>
+      <c r="G21" s="3">
         <v>12149000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>11399000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>8373000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>10830000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>9898000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>10079000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>9530000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>9050000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>8799000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>8353000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>6130000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>5350000</v>
       </c>
-      <c r="R21" s="3"/>
-    </row>
-    <row r="22" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S21" s="3"/>
+    </row>
+    <row r="22" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3634000</v>
+      </c>
+      <c r="E22" s="3">
         <v>3384000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3014000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>2439000</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>2207000</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>2097000</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>2204000</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>2094000</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1986000</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1916000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1527000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1529000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1329000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1244000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>859000</v>
       </c>
-      <c r="R22" s="3"/>
-    </row>
-    <row r="23" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S22" s="3"/>
+    </row>
+    <row r="23" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>5712000</v>
+      </c>
+      <c r="E23" s="3">
         <v>5194000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>4767000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>4078000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>3991000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>920000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>4097000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>3073000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>4266000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>3734000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>3910000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>3763000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>3795000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>2234000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>2465000</v>
       </c>
-      <c r="R23" s="3"/>
-    </row>
-    <row r="24" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S23" s="3"/>
+    </row>
+    <row r="24" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>642000</v>
+      </c>
+      <c r="E24" s="3">
         <v>590000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>438000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>300000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>268000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>-169000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>519000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>448000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>1196000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>1156000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>1256000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>1225000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>1205000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>623000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>752000</v>
       </c>
-      <c r="R24" s="3"/>
-    </row>
-    <row r="25" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S24" s="3"/>
+    </row>
+    <row r="25" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -1500,105 +1548,114 @@
       <c r="Q25" s="3">
         <v>0</v>
       </c>
-      <c r="R25" s="3"/>
-    </row>
-    <row r="26" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R25" s="3">
+        <v>0</v>
+      </c>
+      <c r="S25" s="3"/>
+    </row>
+    <row r="26" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>5070000</v>
+      </c>
+      <c r="E26" s="3">
         <v>4604000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>4329000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>3778000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>3723000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>1089000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>3578000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>2625000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>3070000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>2578000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>2654000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>2538000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>2590000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>1611000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>1713000</v>
       </c>
-      <c r="R26" s="3"/>
-    </row>
-    <row r="27" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S26" s="3"/>
+    </row>
+    <row r="27" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
-        <v>4402000</v>
+        <v>4906000</v>
       </c>
       <c r="E27" s="3">
-        <v>2735000</v>
+        <v>4410000</v>
       </c>
       <c r="F27" s="3">
+        <v>2729000</v>
+      </c>
+      <c r="G27" s="3">
         <v>2444000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>3799000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>1269000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>3687000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>2661000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>3053000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>2560000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>2639000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>2532000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>2579000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>1597000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>1705000</v>
       </c>
-      <c r="R27" s="3"/>
-    </row>
-    <row r="28" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S27" s="3"/>
+    </row>
+    <row r="28" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -1644,57 +1701,63 @@
       <c r="Q28" s="3">
         <v>0</v>
       </c>
-      <c r="R28" s="3"/>
-    </row>
-    <row r="29" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R28" s="3">
+        <v>0</v>
+      </c>
+      <c r="S28" s="3"/>
+    </row>
+    <row r="29" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
+        <v>1000</v>
+      </c>
+      <c r="E29" s="3">
         <v>10000</v>
       </c>
-      <c r="E29" s="3">
+      <c r="F29" s="3">
         <v>-1455000</v>
       </c>
-      <c r="F29" s="3">
+      <c r="G29" s="3">
         <v>-1323000</v>
       </c>
-      <c r="G29" s="3">
+      <c r="H29" s="3">
         <v>-144000</v>
-      </c>
-      <c r="H29" s="3">
-        <v>-7000</v>
       </c>
       <c r="I29" s="3">
         <v>-7000</v>
       </c>
       <c r="J29" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="K29" s="3">
         <v>19000</v>
       </c>
-      <c r="K29" s="3">
+      <c r="L29" s="3">
         <v>-6000</v>
       </c>
-      <c r="L29" s="3">
+      <c r="M29" s="3">
         <v>-408000</v>
       </c>
-      <c r="M29" s="3">
+      <c r="N29" s="3">
         <v>177000</v>
       </c>
-      <c r="N29" s="3">
+      <c r="O29" s="3">
         <v>-649000</v>
       </c>
-      <c r="O29" s="3">
+      <c r="P29" s="3">
         <v>86000</v>
       </c>
-      <c r="P29" s="3">
+      <c r="Q29" s="3">
         <v>207000</v>
       </c>
-      <c r="Q29" s="3">
+      <c r="R29" s="3">
         <v>1000</v>
       </c>
-      <c r="R29" s="3"/>
-    </row>
-    <row r="30" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S29" s="3"/>
+    </row>
+    <row r="30" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -1740,9 +1803,12 @@
       <c r="Q30" s="3">
         <v>0</v>
       </c>
-      <c r="R30" s="3"/>
-    </row>
-    <row r="31" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3"/>
+    </row>
+    <row r="31" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -1788,105 +1854,114 @@
       <c r="Q31" s="3">
         <v>0</v>
       </c>
-      <c r="R31" s="3"/>
-    </row>
-    <row r="32" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R31" s="3">
+        <v>0</v>
+      </c>
+      <c r="S31" s="3"/>
+    </row>
+    <row r="32" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>669000</v>
+      </c>
+      <c r="E32" s="3">
         <v>592000</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>682000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>478000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>685000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1584000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>561000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>462000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>614000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-448000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-389000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-460000</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-254000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-577000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-555000</v>
       </c>
-      <c r="R32" s="3"/>
-    </row>
-    <row r="33" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S32" s="3"/>
+    </row>
+    <row r="33" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>4968000</v>
+      </c>
+      <c r="E33" s="3">
         <v>4524000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>2841000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>2550000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>3908000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>1377000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>3748000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>2666000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>3059000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>2152000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>2816000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>1883000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>2665000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>1804000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>1706000</v>
       </c>
-      <c r="R33" s="3"/>
-    </row>
-    <row r="34" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S33" s="3"/>
+    </row>
+    <row r="34" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -1932,110 +2007,119 @@
       <c r="Q34" s="3">
         <v>0</v>
       </c>
-      <c r="R34" s="3"/>
-    </row>
-    <row r="35" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R34" s="3">
+        <v>0</v>
+      </c>
+      <c r="S34" s="3"/>
+    </row>
+    <row r="35" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>4968000</v>
+      </c>
+      <c r="E35" s="3">
         <v>4524000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>2841000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>2550000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>3908000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>1377000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>3748000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>2666000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>3059000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>2152000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>2816000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>1883000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>2665000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>1804000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>1706000</v>
       </c>
-      <c r="R35" s="3"/>
-    </row>
-    <row r="37" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S35" s="3"/>
+    </row>
+    <row r="37" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>44926</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44561</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44196</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>43830</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>43465</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>43100</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>42735</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>42369</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>42004</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>41639</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>41274</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>40908</v>
       </c>
-      <c r="R38" s="2"/>
-    </row>
-    <row r="39" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S38" s="2"/>
+    </row>
+    <row r="39" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -2054,8 +2138,9 @@
       <c r="P39" s="3"/>
       <c r="Q39" s="3"/>
       <c r="R39" s="3"/>
-    </row>
-    <row r="40" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S39" s="3"/>
+    </row>
+    <row r="40" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -2074,56 +2159,60 @@
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
-    </row>
-    <row r="41" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S40" s="3"/>
+    </row>
+    <row r="41" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>245000</v>
+      </c>
+      <c r="E41" s="3">
         <v>314000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>253000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>409000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>341000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>259000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>311000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>442000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>358000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>392000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>383000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>2036000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1501000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1424000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>2110000</v>
       </c>
-      <c r="R41" s="3"/>
-    </row>
-    <row r="42" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S41" s="3"/>
+    </row>
+    <row r="42" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -2140,374 +2229,398 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>18000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>6000</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>1000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>111000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>6000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>18000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>178000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>333000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>190000</v>
       </c>
-      <c r="R42" s="3"/>
-    </row>
-    <row r="43" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S42" s="3"/>
+    </row>
+    <row r="43" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
-        <v>4672000</v>
+        <v>4230000</v>
       </c>
       <c r="E43" s="3">
+        <v>4610000</v>
+      </c>
+      <c r="F43" s="3">
         <v>4131000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>4415000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>3522000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>3153000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>3060000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>3863000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>3104000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2644000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2263000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2764000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>3005000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2717000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1941000</v>
       </c>
-      <c r="R43" s="3"/>
-    </row>
-    <row r="44" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S43" s="3"/>
+    </row>
+    <row r="44" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>4509000</v>
+        <v>4569000</v>
       </c>
       <c r="E44" s="3">
+        <v>4496000</v>
+      </c>
+      <c r="F44" s="3">
         <v>4292000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>3584000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>3111000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>3167000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>3232000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3084000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>3250000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>3522000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>3746000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>3459000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>6500000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>3223000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1588000</v>
       </c>
-      <c r="R44" s="3"/>
-    </row>
-    <row r="45" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S44" s="3"/>
+    </row>
+    <row r="45" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>3371000</v>
+        <v>2485000</v>
       </c>
       <c r="E45" s="3">
+        <v>3446000</v>
+      </c>
+      <c r="F45" s="3">
         <v>4017000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4732000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>2796000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>1891000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>2332000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>2184000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>1602000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>1370000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>1924000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3662000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>2734000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2425000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1051000</v>
       </c>
-      <c r="R45" s="3"/>
-    </row>
-    <row r="46" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S45" s="3"/>
+    </row>
+    <row r="46" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>11613000</v>
+      </c>
+      <c r="E46" s="3">
         <v>12950000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>12769000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>13222000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>9940000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>8682000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>9163000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>9714000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>8453000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>8039000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>8322000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>11575000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>10516000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>10122000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>6880000</v>
       </c>
-      <c r="R46" s="3"/>
-    </row>
-    <row r="47" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S46" s="3"/>
+    </row>
+    <row r="47" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>330000</v>
+      </c>
+      <c r="E47" s="3">
         <v>353000</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>492000</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>455000</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>457000</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>1519000</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2368000</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>1778000</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>1553000</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>976000</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>506000</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>3038000</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>555000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>554000</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>522000</v>
       </c>
-      <c r="R47" s="3"/>
-    </row>
-    <row r="48" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S47" s="3"/>
+    </row>
+    <row r="48" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
-        <v>122757000</v>
+        <v>129403000</v>
       </c>
       <c r="E48" s="3">
+        <v>121080000</v>
+      </c>
+      <c r="F48" s="3">
         <v>114897000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>111392000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>105290000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>106854000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>102339000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>90181000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>84824000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>82520000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>73779000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>70046000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>170639000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>68558000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>42661000</v>
       </c>
-      <c r="R48" s="3"/>
-    </row>
-    <row r="49" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S48" s="3"/>
+    </row>
+    <row r="49" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
-        <v>19303000</v>
+        <v>19010000</v>
       </c>
       <c r="E49" s="3">
-        <v>19303000</v>
+        <v>19010000</v>
       </c>
       <c r="F49" s="3">
         <v>19303000</v>
       </c>
       <c r="G49" s="3">
+        <v>19303000</v>
+      </c>
+      <c r="H49" s="3">
         <v>19539000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>19598000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>19552000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>19549000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>19626000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>19425000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>16072000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>16321000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>32680000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>16737000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>4212000</v>
       </c>
-      <c r="R49" s="3"/>
-    </row>
-    <row r="50" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S49" s="3"/>
+    </row>
+    <row r="50" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -2553,9 +2666,12 @@
       <c r="Q50" s="3">
         <v>0</v>
       </c>
-      <c r="R50" s="3"/>
-    </row>
-    <row r="51" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R50" s="3">
+        <v>0</v>
+      </c>
+      <c r="S50" s="3"/>
+    </row>
+    <row r="51" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -2601,57 +2717,63 @@
       <c r="Q51" s="3">
         <v>0</v>
       </c>
-      <c r="R51" s="3"/>
-    </row>
-    <row r="52" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R51" s="3">
+        <v>0</v>
+      </c>
+      <c r="S51" s="3"/>
+    </row>
+    <row r="52" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>16726000</v>
+        <v>21001000</v>
       </c>
       <c r="E52" s="3">
+        <v>18730000</v>
+      </c>
+      <c r="F52" s="3">
         <v>15814000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>19069000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>21874000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>13314000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12194000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10553000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>11016000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>21801000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>25562000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>25398000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>17878000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>17885000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8251000</v>
       </c>
-      <c r="R52" s="3"/>
-    </row>
-    <row r="53" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S52" s="3"/>
+    </row>
+    <row r="53" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -2697,57 +2819,63 @@
       <c r="Q53" s="3">
         <v>0</v>
       </c>
-      <c r="R53" s="3"/>
-    </row>
-    <row r="54" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R53" s="3">
+        <v>0</v>
+      </c>
+      <c r="S53" s="3"/>
+    </row>
+    <row r="54" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>195736000</v>
+      </c>
+      <c r="E54" s="3">
         <v>186343000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>176893000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>178086000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>169587000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>162388000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>158838000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>145392000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>137914000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>132761000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>121156000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>120557000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>114779000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>113856000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>62526000</v>
       </c>
-      <c r="R54" s="3"/>
-    </row>
-    <row r="55" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S54" s="3"/>
+    </row>
+    <row r="55" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -2766,8 +2894,9 @@
       <c r="P55" s="3"/>
       <c r="Q55" s="3"/>
       <c r="R55" s="3"/>
-    </row>
-    <row r="56" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S55" s="3"/>
+    </row>
+    <row r="56" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -2786,296 +2915,315 @@
       <c r="P56" s="3"/>
       <c r="Q56" s="3"/>
       <c r="R56" s="3"/>
-    </row>
-    <row r="57" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S56" s="3"/>
+    </row>
+    <row r="57" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
-        <v>5479000</v>
+        <v>5223000</v>
       </c>
       <c r="E57" s="3">
+        <v>5436000</v>
+      </c>
+      <c r="F57" s="3">
         <v>4228000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>4754000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>3531000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>3144000</v>
-      </c>
-      <c r="I57" s="3">
-        <v>3487000</v>
       </c>
       <c r="J57" s="3">
         <v>3487000</v>
       </c>
       <c r="K57" s="3">
+        <v>3487000</v>
+      </c>
+      <c r="L57" s="3">
         <v>3043000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>2994000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>2350000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>2271000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>2391000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>2444000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1433000</v>
       </c>
-      <c r="R57" s="3"/>
-    </row>
-    <row r="58" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S57" s="3"/>
+    </row>
+    <row r="58" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9966000</v>
+      </c>
+      <c r="E58" s="3">
         <v>8141000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>7276000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>8009000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6875000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>7288000</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>6484000</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>6816000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>5407000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>4806000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>5659000</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>5321000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>2943000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>4167000</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>2321000</v>
       </c>
-      <c r="R58" s="3"/>
-    </row>
-    <row r="59" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S58" s="3"/>
+    </row>
+    <row r="59" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>4882000</v>
+        <v>4936000</v>
       </c>
       <c r="E59" s="3">
+        <v>4926000</v>
+      </c>
+      <c r="F59" s="3">
         <v>5034000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5484000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>4071000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>3210000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>2741000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>3378000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>2691000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>3751000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>5506000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>6091000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>3617000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>3418000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1774000</v>
       </c>
-      <c r="R59" s="3"/>
-    </row>
-    <row r="60" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S59" s="3"/>
+    </row>
+    <row r="60" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>21047000</v>
+      </c>
+      <c r="E60" s="3">
         <v>19357000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>17283000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>18873000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>15931000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>16305000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>14752000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>15041000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>12482000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>11551000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>11400000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>11233000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>8644000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>10029000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>5528000</v>
       </c>
-      <c r="R60" s="3"/>
-    </row>
-    <row r="61" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S60" s="3"/>
+    </row>
+    <row r="61" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>81141000</v>
+      </c>
+      <c r="E61" s="3">
         <v>77297000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>73369000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>66749000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>61388000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>56965000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>56417000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>51123000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>49035000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>45576000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>36842000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>37061000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>38152000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>36351000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>18679000</v>
       </c>
-      <c r="R61" s="3"/>
-    </row>
-    <row r="62" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S61" s="3"/>
+    </row>
+    <row r="62" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>26787000</v>
+      </c>
+      <c r="E62" s="3">
         <v>25681000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>24149000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>28966000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>30065000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>29034000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>29282000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>26032000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>26397000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>34593000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>33949000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>33004000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>26664000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>26535000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>15454000</v>
       </c>
-      <c r="R62" s="3"/>
-    </row>
-    <row r="63" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S62" s="3"/>
+    </row>
+    <row r="63" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -3121,9 +3269,12 @@
       <c r="Q63" s="3">
         <v>0</v>
       </c>
-      <c r="R63" s="3"/>
-    </row>
-    <row r="64" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R63" s="3">
+        <v>0</v>
+      </c>
+      <c r="S63" s="3"/>
+    </row>
+    <row r="64" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -3169,9 +3320,12 @@
       <c r="Q64" s="3">
         <v>0</v>
       </c>
-      <c r="R64" s="3"/>
-    </row>
-    <row r="65" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R64" s="3">
+        <v>0</v>
+      </c>
+      <c r="S64" s="3"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -3217,57 +3371,63 @@
       <c r="Q65" s="3">
         <v>0</v>
       </c>
-      <c r="R65" s="3"/>
-    </row>
-    <row r="66" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R65" s="3">
+        <v>0</v>
+      </c>
+      <c r="S65" s="3"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>142717000</v>
+      </c>
+      <c r="E66" s="3">
         <v>135087000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>126706000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>126233000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>118451000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>113204000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>110887000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>101558000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>96177000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>91728000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>81429000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>79682000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>73449000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>72993000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>39754000</v>
       </c>
-      <c r="R66" s="3"/>
-    </row>
-    <row r="67" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S66" s="3"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -3286,8 +3446,9 @@
       <c r="P67" s="3"/>
       <c r="Q67" s="3"/>
       <c r="R67" s="3"/>
-    </row>
-    <row r="68" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S67" s="3"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -3333,9 +3494,12 @@
       <c r="Q68" s="3">
         <v>0</v>
       </c>
-      <c r="R68" s="3"/>
-    </row>
-    <row r="69" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R68" s="3">
+        <v>0</v>
+      </c>
+      <c r="S68" s="3"/>
+    </row>
+    <row r="69" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -3381,9 +3545,12 @@
       <c r="Q69" s="3">
         <v>0</v>
       </c>
-      <c r="R69" s="3"/>
-    </row>
-    <row r="70" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R69" s="3">
+        <v>0</v>
+      </c>
+      <c r="S69" s="3"/>
+    </row>
+    <row r="70" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -3391,7 +3558,7 @@
         <v>973000</v>
       </c>
       <c r="E70" s="3">
-        <v>1962000</v>
+        <v>973000</v>
       </c>
       <c r="F70" s="3">
         <v>1962000</v>
@@ -3406,7 +3573,7 @@
         <v>1962000</v>
       </c>
       <c r="J70" s="3">
-        <v>0</v>
+        <v>1962000</v>
       </c>
       <c r="K70" s="3">
         <v>0</v>
@@ -3429,9 +3596,12 @@
       <c r="Q70" s="3">
         <v>0</v>
       </c>
-      <c r="R70" s="3"/>
-    </row>
-    <row r="71" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R70" s="3">
+        <v>0</v>
+      </c>
+      <c r="S70" s="3"/>
+    </row>
+    <row r="71" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -3477,57 +3647,63 @@
       <c r="Q71" s="3">
         <v>0</v>
       </c>
-      <c r="R71" s="3"/>
-    </row>
-    <row r="72" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R71" s="3">
+        <v>0</v>
+      </c>
+      <c r="S71" s="3"/>
+    </row>
+    <row r="72" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>5056000</v>
+      </c>
+      <c r="E72" s="3">
         <v>3431000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2235000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2637000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>3265000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2471000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>4108000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>3113000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>3013000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2384000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2564000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>2012000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>2363000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1889000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1873000</v>
       </c>
-      <c r="R72" s="3"/>
-    </row>
-    <row r="73" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S72" s="3"/>
+    </row>
+    <row r="73" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -3573,9 +3749,12 @@
       <c r="Q73" s="3">
         <v>0</v>
       </c>
-      <c r="R73" s="3"/>
-    </row>
-    <row r="74" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R73" s="3">
+        <v>0</v>
+      </c>
+      <c r="S73" s="3"/>
+    </row>
+    <row r="74" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -3621,9 +3800,12 @@
       <c r="Q74" s="3">
         <v>0</v>
       </c>
-      <c r="R74" s="3"/>
-    </row>
-    <row r="75" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R74" s="3">
+        <v>0</v>
+      </c>
+      <c r="S74" s="3"/>
+    </row>
+    <row r="75" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -3669,57 +3851,63 @@
       <c r="Q75" s="3">
         <v>0</v>
       </c>
-      <c r="R75" s="3"/>
-    </row>
-    <row r="76" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R75" s="3">
+        <v>0</v>
+      </c>
+      <c r="S75" s="3"/>
+    </row>
+    <row r="76" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>50869000</v>
+      </c>
+      <c r="E76" s="3">
         <v>49154000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>47150000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>47360000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>47334000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>46002000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>44860000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>43817000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>41739000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>41033000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>39727000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>40875000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>41330000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>40863000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>22772000</v>
       </c>
-      <c r="R76" s="3"/>
-    </row>
-    <row r="77" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="S76" s="3"/>
+    </row>
+    <row r="77" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -3765,110 +3953,119 @@
       <c r="Q77" s="3">
         <v>0</v>
       </c>
-      <c r="R77" s="3"/>
-    </row>
-    <row r="79" spans="2:18" x14ac:dyDescent="0.2">
+      <c r="R77" s="3">
+        <v>0</v>
+      </c>
+      <c r="S77" s="3"/>
+    </row>
+    <row r="79" spans="2:19" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:18" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:19" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>44926</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44561</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44196</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>43830</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>43465</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>43100</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>42735</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>42369</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>42004</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>41639</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>41274</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>40908</v>
       </c>
-      <c r="R80" s="2"/>
-    </row>
-    <row r="81" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S80" s="2"/>
+    </row>
+    <row r="81" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>4968000</v>
+      </c>
+      <c r="E81" s="3">
         <v>4524000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>2841000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>2550000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>3908000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>1377000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>3748000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>2666000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>3059000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>2152000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>2816000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>1883000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>2665000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>1804000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>1706000</v>
       </c>
-      <c r="R81" s="3"/>
-    </row>
-    <row r="82" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S81" s="3"/>
+    </row>
+    <row r="82" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -3887,56 +4084,60 @@
       <c r="P82" s="3"/>
       <c r="Q82" s="3"/>
       <c r="R82" s="3"/>
-    </row>
-    <row r="83" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S82" s="3"/>
+    </row>
+    <row r="83" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>7230000</v>
+      </c>
+      <c r="E83" s="3">
         <v>5985000</v>
       </c>
-      <c r="E83" s="3">
-        <v>5561000</v>
-      </c>
       <c r="F83" s="3">
+        <v>6084000</v>
+      </c>
+      <c r="G83" s="3">
         <v>5843000</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>5663000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>5486000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>5176000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>4696000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>4046000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>3880000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3613000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>3507000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>3229000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>2652000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>2026000</v>
       </c>
-      <c r="R83" s="3"/>
-    </row>
-    <row r="84" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S83" s="3"/>
+    </row>
+    <row r="84" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -3982,9 +4183,12 @@
       <c r="Q84" s="3">
         <v>0</v>
       </c>
-      <c r="R84" s="3"/>
-    </row>
-    <row r="85" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R84" s="3">
+        <v>0</v>
+      </c>
+      <c r="S84" s="3"/>
+    </row>
+    <row r="85" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -4030,9 +4234,12 @@
       <c r="Q85" s="3">
         <v>0</v>
       </c>
-      <c r="R85" s="3"/>
-    </row>
-    <row r="86" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R85" s="3">
+        <v>0</v>
+      </c>
+      <c r="S85" s="3"/>
+    </row>
+    <row r="86" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -4078,9 +4285,12 @@
       <c r="Q86" s="3">
         <v>0</v>
       </c>
-      <c r="R86" s="3"/>
-    </row>
-    <row r="87" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R86" s="3">
+        <v>0</v>
+      </c>
+      <c r="S86" s="3"/>
+    </row>
+    <row r="87" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -4126,9 +4336,12 @@
       <c r="Q87" s="3">
         <v>0</v>
       </c>
-      <c r="R87" s="3"/>
-    </row>
-    <row r="88" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R87" s="3">
+        <v>0</v>
+      </c>
+      <c r="S87" s="3"/>
+    </row>
+    <row r="88" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -4174,57 +4387,63 @@
       <c r="Q88" s="3">
         <v>0</v>
       </c>
-      <c r="R88" s="3"/>
-    </row>
-    <row r="89" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R88" s="3">
+        <v>0</v>
+      </c>
+      <c r="S88" s="3"/>
+    </row>
+    <row r="89" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>12330000</v>
+      </c>
+      <c r="E89" s="3">
         <v>12328000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>9878000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>5927000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>8290000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>8856000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>8209000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>7186000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>6624000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>7337000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>7775000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>6038000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6382000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>5244000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>3672000</v>
       </c>
-      <c r="R89" s="3"/>
-    </row>
-    <row r="90" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S89" s="3"/>
+    </row>
+    <row r="90" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -4243,56 +4462,60 @@
       <c r="P90" s="3"/>
       <c r="Q90" s="3"/>
       <c r="R90" s="3"/>
-    </row>
-    <row r="91" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S90" s="3"/>
+    </row>
+    <row r="91" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14024000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-12280000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-12604000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11367000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9715000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9907000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11122000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9389000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8052000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-7901000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-6766000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-5384000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5526000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5501000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4363000</v>
       </c>
-      <c r="R91" s="3"/>
-    </row>
-    <row r="92" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S91" s="3"/>
+    </row>
+    <row r="92" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -4338,9 +4561,12 @@
       <c r="Q92" s="3">
         <v>0</v>
       </c>
-      <c r="R92" s="3"/>
-    </row>
-    <row r="93" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R92" s="3">
+        <v>0</v>
+      </c>
+      <c r="S92" s="3"/>
+    </row>
+    <row r="93" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -4386,57 +4612,63 @@
       <c r="Q93" s="3">
         <v>0</v>
       </c>
-      <c r="R93" s="3"/>
-    </row>
-    <row r="94" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R93" s="3">
+        <v>0</v>
+      </c>
+      <c r="S93" s="3"/>
+    </row>
+    <row r="94" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-14338000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-13123000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-12475000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-11973000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-10935000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10604000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11957000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-10060000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8442000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11528000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5277000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5373000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-4978000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-6197000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4434000</v>
       </c>
-      <c r="R94" s="3"/>
-    </row>
-    <row r="95" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S94" s="3"/>
+    </row>
+    <row r="95" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -4455,8 +4687,9 @@
       <c r="P95" s="3"/>
       <c r="Q95" s="3"/>
       <c r="R95" s="3"/>
-    </row>
-    <row r="96" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S95" s="3"/>
+    </row>
+    <row r="96" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -4464,47 +4697,50 @@
         <v>0</v>
       </c>
       <c r="E96" s="3">
+        <v>0</v>
+      </c>
+      <c r="F96" s="3">
         <v>3138000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>3073000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>3008000</v>
       </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
       <c r="I96" s="3">
         <v>0</v>
       </c>
       <c r="J96" s="3">
+        <v>0</v>
+      </c>
+      <c r="K96" s="3">
         <v>2471000</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>2450000</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2332000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2254000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2234000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2188000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-1752000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-1329000</v>
       </c>
-      <c r="R96" s="3"/>
-    </row>
-    <row r="97" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S96" s="3"/>
+    </row>
+    <row r="97" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -4550,9 +4786,12 @@
       <c r="Q97" s="3">
         <v>0</v>
       </c>
-      <c r="R97" s="3"/>
-    </row>
-    <row r="98" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R97" s="3">
+        <v>0</v>
+      </c>
+      <c r="S97" s="3"/>
+    </row>
+    <row r="98" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -4598,9 +4837,12 @@
       <c r="Q98" s="3">
         <v>0</v>
       </c>
-      <c r="R98" s="3"/>
-    </row>
-    <row r="99" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R98" s="3">
+        <v>0</v>
+      </c>
+      <c r="S98" s="3"/>
+    </row>
+    <row r="99" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -4646,57 +4888,63 @@
       <c r="Q99" s="3">
         <v>0</v>
       </c>
-      <c r="R99" s="3"/>
-    </row>
-    <row r="100" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R99" s="3">
+        <v>0</v>
+      </c>
+      <c r="S99" s="3"/>
+    </row>
+    <row r="100" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>1950000</v>
+      </c>
+      <c r="E100" s="3">
         <v>859000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>2351000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>6129000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2609000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1731000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>3730000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>2960000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>1782000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>4251000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-2578000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-678000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-1327000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>267000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1202000</v>
       </c>
-      <c r="R100" s="3"/>
-    </row>
-    <row r="101" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="S100" s="3"/>
+    </row>
+    <row r="101" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -4724,8 +4972,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -4742,55 +4990,61 @@
       <c r="Q101" s="3">
         <v>0</v>
       </c>
-      <c r="R101" s="3"/>
-    </row>
-    <row r="102" spans="3:18" x14ac:dyDescent="0.2">
+      <c r="R101" s="3">
+        <v>0</v>
+      </c>
+      <c r="S101" s="3"/>
+    </row>
+    <row r="102" spans="3:19" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-58000</v>
+      </c>
+      <c r="E102" s="3">
         <v>64000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-246000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>83000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-36000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-17000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-18000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>86000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-36000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>60000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-80000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-13000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>77000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-686000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>440000</v>
       </c>
-      <c r="R102" s="3"/>
+      <c r="S102" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
